--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>360199</v>
+        <v>360215</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>0.5786</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>339129</v>
+        <v>339229</v>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5357</v>
+        <v>0.5356</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>371486</v>
+        <v>371580</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="G11" t="n">
         <v>0.3349</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>57.53%</t>
+          <t>57.55%</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>187.5:1</t>
+          <t>187.6:1</t>
         </is>
       </c>
     </row>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>472642</v>
+        <v>472753</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4944</v>
+        <v>0.4943</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>37.4:1</t>
+          <t>37.5:1</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>334864</v>
+        <v>335169</v>
       </c>
       <c r="F13" t="n">
-        <v>293</v>
+        <v>598</v>
       </c>
       <c r="G13" t="n">
         <v>0.0998</v>
@@ -952,12 +952,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>50.89%</t>
+          <t>50.90%</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>159.4:1</t>
+          <t>159.5:1</t>
         </is>
       </c>
     </row>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>136740</v>
+        <v>136756</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
         <v>0.06619999999999999</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.92%</t>
+          <t>32.90%</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>5259.2:1</t>
+          <t>5259.8:1</t>
         </is>
       </c>
     </row>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>436907</v>
+        <v>437216</v>
       </c>
       <c r="F15" t="n">
-        <v>305</v>
+        <v>614</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1096</v>
+        <v>0.1095</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>262.2:1</t>
+          <t>262.4:1</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>178470</v>
+        <v>178585</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="G16" t="n">
         <v>0.1171</v>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>45.60%</t>
+          <t>45.64%</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1784.7:1</t>
+          <t>1785.8:1</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>142818</v>
+        <v>142834</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
         <v>0.0964</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>634.7:1</t>
+          <t>634.8:1</t>
         </is>
       </c>
     </row>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>385978</v>
+        <v>386301</v>
       </c>
       <c r="F18" t="n">
-        <v>312</v>
+        <v>635</v>
       </c>
       <c r="G18" t="n">
         <v>0.1101</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1347,48 +1347,48 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>38.95%</t>
+          <t>38.97%</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>219.4:1</t>
+          <t>219.6:1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BV1xwYQ6zEcC</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>红色防吞2</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-12 13:43:19</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13603</v>
+        <v>37912</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0042</v>
+        <v>2.1415</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>常规更新</t>
+          <t>爆火潜力</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1396,78 +1396,78 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>32.20%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>20.09%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>29.57%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>11.73%</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>91.83%</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>13603.0:1</t>
+          <t>78.5:1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>红色防吞3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-13 20:48:29</t>
+          <t>2026-09-15 01:28:46</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37912</v>
+        <v>11218</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1415</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>爆火潜力</t>
+          <t>常规更新</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1475,49 +1475,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.20%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20.09%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29.57%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>11.73%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>91.83%</t>
+          <t>150.00%</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>78.5:1</t>
+          <t>11218.0:1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BV1erbv6AEeL</t>
+          <t>BV1C8gW6KEkX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1527,22 +1527,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-18 00:34:17</t>
+          <t>2026-08-14 00:43:15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>161502</v>
+        <v>208268</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.482</v>
+        <v>0.2427</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1554,42 +1554,42 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>73.85%</t>
+          <t>53.34%</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>133.9:1</t>
+          <t>208268.0:1</t>
         </is>
       </c>
     </row>
@@ -1675,32 +1675,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BV1vdbC6RE8S</t>
+          <t>BV1erbv6AEeL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Euphoria欢欣丨张桂源</t>
+          <t>Split0511-张桂源</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+          <t>【张桂源】 刺 4k 横版focus</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:48</t>
+          <t>2026-08-18 00:34:17</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106282</v>
+        <v>161502</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6821</v>
+        <v>0.482</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1712,78 +1712,78 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.20%</t>
+          <t>7.30%</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>7.39%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>100.28%</t>
+          <t>73.85%</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>87.5:1</t>
+          <t>133.9:1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BV1C8gW6KEkX</t>
+          <t>BV1qiBkBGEoj</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>wish0511_张桂源</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-14 00:43:15</t>
+          <t>2025-12-27 16:42:34</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208268</v>
+        <v>980765</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2427</v>
+        <v>0.1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>爆火潜力</t>
+          <t>优质内容</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1791,78 +1791,78 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>53.34%</t>
+          <t>65.96%</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>208268.0:1</t>
+          <t>682.5:1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BV1qiBkBGEoj</t>
+          <t>BV1vdbC6RE8S</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wish0511_张桂源</t>
+          <t>Euphoria欢欣丨张桂源</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-27 16:42:34</t>
+          <t>2026-08-15 23:00:48</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>980765</v>
+        <v>106282</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0.6821</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>优质内容</t>
+          <t>爆火潜力</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1870,49 +1870,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>9.20%</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>9.74%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>65.96%</t>
+          <t>100.28%</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>682.5:1</t>
+          <t>87.5:1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1xwYQ6zEcC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>红色防吞3</t>
+          <t>红色防吞2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-15 01:28:46</t>
+          <t>2026-09-12 13:43:19</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11131</v>
+        <v>13603</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>150.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11131.0:1</t>
+          <t>13603.0:1</t>
         </is>
       </c>
     </row>
@@ -3162,44 +3162,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1xwYQ6zEcC</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>红色防吞2</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:43:19</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13600</v>
+        <v>37911</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>12208</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>11210</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>7617</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>4447</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3216,50 +3216,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1xwYQ6zEcC</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>红色防吞2</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:43:19</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13603</v>
+        <v>37912</v>
       </c>
       <c r="G23" t="n">
+        <v>12209</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11212</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7617</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4447</v>
+      </c>
+      <c r="K23" t="n">
+        <v>483</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3270,44 +3270,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>红色防吞3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-13 20:48:29</t>
+          <t>2026-09-15 01:28:46</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37911</v>
+        <v>11050</v>
       </c>
       <c r="G24" t="n">
-        <v>12208</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>11210</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>7617</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>4447</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3324,50 +3324,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>红色防吞3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-13 20:48:29</t>
+          <t>2026-09-15 01:28:46</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>37912</v>
+        <v>11131</v>
       </c>
       <c r="G25" t="n">
-        <v>12209</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>11212</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>7617</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>4447</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
@@ -3378,44 +3378,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1erbv6AEeL</t>
+          <t>BV1xwYQ6zEcC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
+          <t>红色防吞2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-18 00:34:17</t>
+          <t>2026-09-12 13:43:19</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>161498</v>
+        <v>13600</v>
       </c>
       <c r="G26" t="n">
-        <v>11782</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>8702</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11939</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>1007</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>4191</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3432,50 +3432,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1erbv6AEeL</t>
+          <t>BV1xwYQ6zEcC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
+          <t>红色防吞2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-18 00:34:17</t>
+          <t>2026-09-12 13:43:19</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>161502</v>
+        <v>13603</v>
       </c>
       <c r="G27" t="n">
-        <v>11783</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>8702</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>11939</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>1007</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>4191</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -3486,44 +3486,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1WhgW6iEg4</t>
+          <t>BV1erbv6AEeL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+          <t>【张桂源】 刺 4k 横版focus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>序言丨张桂源</t>
+          <t>Split0511-张桂源</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-14 00:50:50</t>
+          <t>2026-08-18 00:34:17</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>141754</v>
+        <v>161498</v>
       </c>
       <c r="G28" t="n">
-        <v>7525</v>
+        <v>11782</v>
       </c>
       <c r="H28" t="n">
-        <v>5453</v>
+        <v>8702</v>
       </c>
       <c r="I28" t="n">
-        <v>5614</v>
+        <v>11939</v>
       </c>
       <c r="J28" t="n">
-        <v>424</v>
+        <v>1007</v>
       </c>
       <c r="K28" t="n">
-        <v>512</v>
+        <v>1206</v>
       </c>
       <c r="L28" t="n">
-        <v>2284</v>
+        <v>4191</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3540,50 +3540,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1WhgW6iEg4</t>
+          <t>BV1erbv6AEeL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+          <t>【张桂源】 刺 4k 横版focus</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>序言丨张桂源</t>
+          <t>Split0511-张桂源</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-14 00:50:50</t>
+          <t>2026-08-18 00:34:17</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>141757</v>
+        <v>161502</v>
       </c>
       <c r="G29" t="n">
-        <v>7526</v>
+        <v>11783</v>
       </c>
       <c r="H29" t="n">
-        <v>5453</v>
+        <v>8702</v>
       </c>
       <c r="I29" t="n">
-        <v>5614</v>
+        <v>11939</v>
       </c>
       <c r="J29" t="n">
-        <v>424</v>
+        <v>1007</v>
       </c>
       <c r="K29" t="n">
-        <v>512</v>
+        <v>1206</v>
       </c>
       <c r="L29" t="n">
-        <v>2284</v>
+        <v>4191</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -3594,44 +3594,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1vdbC6RE8S</t>
+          <t>BV1WhgW6iEg4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Euphoria欢欣丨张桂源</t>
+          <t>序言丨张桂源</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:48</t>
+          <t>2026-08-14 00:50:50</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>106282</v>
+        <v>141754</v>
       </c>
       <c r="G30" t="n">
-        <v>9774</v>
+        <v>7525</v>
       </c>
       <c r="H30" t="n">
-        <v>9801</v>
+        <v>5453</v>
       </c>
       <c r="I30" t="n">
-        <v>10347</v>
+        <v>5614</v>
       </c>
       <c r="J30" t="n">
-        <v>932</v>
+        <v>424</v>
       </c>
       <c r="K30" t="n">
-        <v>1214</v>
+        <v>512</v>
       </c>
       <c r="L30" t="n">
-        <v>3772</v>
+        <v>2284</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3648,50 +3648,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1vdbC6RE8S</t>
+          <t>BV1WhgW6iEg4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Euphoria欢欣丨张桂源</t>
+          <t>序言丨张桂源</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:48</t>
+          <t>2026-08-14 00:50:50</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>106282</v>
+        <v>141757</v>
       </c>
       <c r="G31" t="n">
-        <v>9774</v>
+        <v>7526</v>
       </c>
       <c r="H31" t="n">
-        <v>9801</v>
+        <v>5453</v>
       </c>
       <c r="I31" t="n">
-        <v>10347</v>
+        <v>5614</v>
       </c>
       <c r="J31" t="n">
-        <v>932</v>
+        <v>424</v>
       </c>
       <c r="K31" t="n">
-        <v>1214</v>
+        <v>512</v>
       </c>
       <c r="L31" t="n">
-        <v>3772</v>
+        <v>2284</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -3702,44 +3702,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1C8gW6KEkX</t>
+          <t>BV1vdbC6RE8S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Euphoria欢欣丨张桂源</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-14 00:43:15</t>
+          <t>2026-08-15 23:00:48</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>208266</v>
+        <v>106282</v>
       </c>
       <c r="G32" t="n">
-        <v>8985</v>
+        <v>9774</v>
       </c>
       <c r="H32" t="n">
-        <v>4793</v>
+        <v>9801</v>
       </c>
       <c r="I32" t="n">
-        <v>6808</v>
+        <v>10347</v>
       </c>
       <c r="J32" t="n">
-        <v>447</v>
+        <v>932</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="L32" t="n">
-        <v>9316</v>
+        <v>3772</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3756,50 +3756,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1C8gW6KEkX</t>
+          <t>BV1vdbC6RE8S</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Euphoria欢欣丨张桂源</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-14 00:43:15</t>
+          <t>2026-08-15 23:00:48</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>208268</v>
+        <v>106282</v>
       </c>
       <c r="G33" t="n">
-        <v>8985</v>
+        <v>9774</v>
       </c>
       <c r="H33" t="n">
-        <v>4793</v>
+        <v>9801</v>
       </c>
       <c r="I33" t="n">
-        <v>6808</v>
+        <v>10347</v>
       </c>
       <c r="J33" t="n">
-        <v>447</v>
+        <v>932</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="L33" t="n">
-        <v>9316</v>
+        <v>3772</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3810,44 +3810,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1qiBkBGEoj</t>
+          <t>BV1C8gW6KEkX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>wish0511_张桂源</t>
+          <t>Split0511-张桂源</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-12-27 16:42:34</t>
+          <t>2026-08-14 00:43:15</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>980762</v>
+        <v>208266</v>
       </c>
       <c r="G34" t="n">
-        <v>16726</v>
+        <v>8985</v>
       </c>
       <c r="H34" t="n">
-        <v>11033</v>
+        <v>4793</v>
       </c>
       <c r="I34" t="n">
-        <v>14544</v>
+        <v>6808</v>
       </c>
       <c r="J34" t="n">
-        <v>1299</v>
+        <v>447</v>
       </c>
       <c r="K34" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>4834</v>
+        <v>9316</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3864,50 +3864,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1qiBkBGEoj</t>
+          <t>BV1C8gW6KEkX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wish0511_张桂源</t>
+          <t>Split0511-张桂源</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-12-27 16:42:34</t>
+          <t>2026-08-14 00:43:15</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>980765</v>
+        <v>208268</v>
       </c>
       <c r="G35" t="n">
-        <v>16726</v>
+        <v>8985</v>
       </c>
       <c r="H35" t="n">
-        <v>11033</v>
+        <v>4793</v>
       </c>
       <c r="I35" t="n">
-        <v>14545</v>
+        <v>6808</v>
       </c>
       <c r="J35" t="n">
-        <v>1299</v>
+        <v>447</v>
       </c>
       <c r="K35" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>4834</v>
+        <v>9316</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3918,44 +3918,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qiBkBGEoj</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>红色防吞3</t>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>wish0511_张桂源</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-15 01:28:46</t>
+          <t>2025-12-27 16:42:34</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11050</v>
+        <v>980762</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>16726</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>11033</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>14544</v>
       </c>
       <c r="J36" t="n">
-        <v>12</v>
+        <v>1299</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4834</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -3972,50 +3972,50 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qiBkBGEoj</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>红色防吞3</t>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>wish0511_张桂源</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-15 01:28:46</t>
+          <t>2025-12-27 16:42:34</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11131</v>
+        <v>980765</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>16726</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>11033</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>14545</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>1299</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4834</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4215,61 +4215,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>underthepoplar</t>
+          <t>关键时刻来瓶尖叫</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-13 22:44:57</t>
+          <t>2026-08-13 23:45:41</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>339040</v>
+        <v>360215</v>
       </c>
       <c r="G4" t="n">
-        <v>26695</v>
+        <v>30865</v>
       </c>
       <c r="H4" t="n">
-        <v>16876</v>
+        <v>23642</v>
       </c>
       <c r="I4" t="n">
-        <v>19119</v>
+        <v>23321</v>
       </c>
       <c r="J4" t="n">
-        <v>6422</v>
+        <v>7168</v>
       </c>
       <c r="K4" t="n">
-        <v>7611</v>
+        <v>5239</v>
       </c>
       <c r="L4" t="n">
-        <v>8928</v>
+        <v>8735</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4293,16 +4293,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>339129</v>
+        <v>339040</v>
       </c>
       <c r="G5" t="n">
-        <v>26697</v>
+        <v>26695</v>
       </c>
       <c r="H5" t="n">
-        <v>16878</v>
+        <v>16876</v>
       </c>
       <c r="I5" t="n">
-        <v>19120</v>
+        <v>19119</v>
       </c>
       <c r="J5" t="n">
         <v>6422</v>
@@ -4317,23 +4317,23 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4343,51 +4343,51 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-16 23:54:18</t>
+          <t>2026-08-13 22:44:57</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>371396</v>
+        <v>339129</v>
       </c>
       <c r="G6" t="n">
-        <v>21259</v>
+        <v>26697</v>
       </c>
       <c r="H6" t="n">
-        <v>12230</v>
+        <v>16878</v>
       </c>
       <c r="I6" t="n">
-        <v>17509</v>
+        <v>19120</v>
       </c>
       <c r="J6" t="n">
-        <v>3425</v>
+        <v>6422</v>
       </c>
       <c r="K6" t="n">
-        <v>1981</v>
+        <v>7611</v>
       </c>
       <c r="L6" t="n">
-        <v>3102</v>
+        <v>8928</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4397,35 +4397,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-16 23:54:18</t>
+          <t>2026-08-13 22:44:57</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>371486</v>
+        <v>339229</v>
       </c>
       <c r="G7" t="n">
-        <v>21262</v>
+        <v>26700</v>
       </c>
       <c r="H7" t="n">
-        <v>12232</v>
+        <v>16880</v>
       </c>
       <c r="I7" t="n">
-        <v>17510</v>
+        <v>19121</v>
       </c>
       <c r="J7" t="n">
-        <v>3425</v>
+        <v>6422</v>
       </c>
       <c r="K7" t="n">
-        <v>1981</v>
+        <v>7611</v>
       </c>
       <c r="L7" t="n">
-        <v>3102</v>
+        <v>8928</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -4436,44 +4436,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV1xebR6zEkr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kismet丨杨博文</t>
+          <t>underthepoplar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-16 22:13:05</t>
+          <t>2026-08-16 23:54:18</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>472541</v>
+        <v>371396</v>
       </c>
       <c r="G8" t="n">
-        <v>38141</v>
+        <v>21259</v>
       </c>
       <c r="H8" t="n">
-        <v>17267</v>
+        <v>12230</v>
       </c>
       <c r="I8" t="n">
-        <v>25701</v>
+        <v>17509</v>
       </c>
       <c r="J8" t="n">
-        <v>6212</v>
+        <v>3425</v>
       </c>
       <c r="K8" t="n">
-        <v>12622</v>
+        <v>1981</v>
       </c>
       <c r="L8" t="n">
-        <v>14938</v>
+        <v>3102</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4490,66 +4490,66 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV1xebR6zEkr</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kismet丨杨博文</t>
+          <t>underthepoplar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-16 22:13:05</t>
+          <t>2026-08-16 23:54:18</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>472642</v>
+        <v>371486</v>
       </c>
       <c r="G9" t="n">
-        <v>38141</v>
+        <v>21262</v>
       </c>
       <c r="H9" t="n">
-        <v>17267</v>
+        <v>12232</v>
       </c>
       <c r="I9" t="n">
-        <v>25704</v>
+        <v>17510</v>
       </c>
       <c r="J9" t="n">
-        <v>6213</v>
+        <v>3425</v>
       </c>
       <c r="K9" t="n">
-        <v>12622</v>
+        <v>1981</v>
       </c>
       <c r="L9" t="n">
-        <v>14938</v>
+        <v>3102</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1xebR6zEkr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4559,197 +4559,197 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-22 04:21:09</t>
+          <t>2026-08-16 23:54:18</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>334571</v>
+        <v>371580</v>
       </c>
       <c r="G10" t="n">
-        <v>5745</v>
+        <v>21263</v>
       </c>
       <c r="H10" t="n">
-        <v>2924</v>
+        <v>12236</v>
       </c>
       <c r="I10" t="n">
-        <v>3460</v>
+        <v>17511</v>
       </c>
       <c r="J10" t="n">
-        <v>881</v>
+        <v>3425</v>
       </c>
       <c r="K10" t="n">
-        <v>2101</v>
+        <v>1981</v>
       </c>
       <c r="L10" t="n">
-        <v>738</v>
+        <v>3102</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>underthepoplar</t>
+          <t>Kismet丨杨博文</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-22 04:21:09</t>
+          <t>2026-08-16 22:13:05</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>334864</v>
+        <v>472541</v>
       </c>
       <c r="G11" t="n">
-        <v>5746</v>
+        <v>38141</v>
       </c>
       <c r="H11" t="n">
-        <v>2924</v>
+        <v>17267</v>
       </c>
       <c r="I11" t="n">
-        <v>3462</v>
+        <v>25701</v>
       </c>
       <c r="J11" t="n">
-        <v>882</v>
+        <v>6212</v>
       </c>
       <c r="K11" t="n">
-        <v>2101</v>
+        <v>12622</v>
       </c>
       <c r="L11" t="n">
-        <v>738</v>
+        <v>14938</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>61strawberry</t>
+          <t>Kismet丨杨博文</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-17 06:33:44</t>
+          <t>2026-08-16 22:13:05</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>136722</v>
+        <v>472642</v>
       </c>
       <c r="G12" t="n">
-        <v>2318</v>
+        <v>38141</v>
       </c>
       <c r="H12" t="n">
-        <v>763</v>
+        <v>17267</v>
       </c>
       <c r="I12" t="n">
-        <v>1654</v>
+        <v>25704</v>
       </c>
       <c r="J12" t="n">
-        <v>26</v>
+        <v>6213</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>12622</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>14938</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>61strawberry</t>
+          <t>Kismet丨杨博文</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-17 06:33:44</t>
+          <t>2026-08-16 22:13:05</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>136740</v>
+        <v>472753</v>
       </c>
       <c r="G13" t="n">
-        <v>2318</v>
+        <v>38143</v>
       </c>
       <c r="H13" t="n">
-        <v>763</v>
+        <v>17267</v>
       </c>
       <c r="I13" t="n">
-        <v>1654</v>
+        <v>25705</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>6213</v>
       </c>
       <c r="K13" t="n">
-        <v>26</v>
+        <v>12623</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>14938</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -4760,44 +4760,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV15egs6pEJp</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LOST_杨博文</t>
+          <t>underthepoplar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-13 23:03:07</t>
+          <t>2026-08-22 04:21:09</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>436602</v>
+        <v>334571</v>
       </c>
       <c r="G14" t="n">
-        <v>9953</v>
+        <v>5745</v>
       </c>
       <c r="H14" t="n">
-        <v>2657</v>
+        <v>2924</v>
       </c>
       <c r="I14" t="n">
-        <v>7451</v>
+        <v>3460</v>
       </c>
       <c r="J14" t="n">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="K14" t="n">
-        <v>1666</v>
+        <v>2101</v>
       </c>
       <c r="L14" t="n">
-        <v>773</v>
+        <v>738</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -4814,260 +4814,260 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV15egs6pEJp</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LOST_杨博文</t>
+          <t>underthepoplar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-13 23:03:07</t>
+          <t>2026-08-22 04:21:09</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>436907</v>
+        <v>334864</v>
       </c>
       <c r="G15" t="n">
-        <v>9956</v>
+        <v>5746</v>
       </c>
       <c r="H15" t="n">
-        <v>2659</v>
+        <v>2924</v>
       </c>
       <c r="I15" t="n">
-        <v>7455</v>
+        <v>3462</v>
       </c>
       <c r="J15" t="n">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="K15" t="n">
-        <v>1666</v>
+        <v>2101</v>
       </c>
       <c r="L15" t="n">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
+          <t>underthepoplar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-14 01:41:46</t>
+          <t>2026-08-22 04:21:09</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>178375</v>
+        <v>335169</v>
       </c>
       <c r="G16" t="n">
-        <v>4444</v>
+        <v>5749</v>
       </c>
       <c r="H16" t="n">
-        <v>2027</v>
+        <v>2926</v>
       </c>
       <c r="I16" t="n">
-        <v>3316</v>
+        <v>3462</v>
       </c>
       <c r="J16" t="n">
-        <v>377</v>
+        <v>882</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>2101</v>
       </c>
       <c r="L16" t="n">
-        <v>274</v>
+        <v>738</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
+          <t>61strawberry</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-14 01:41:46</t>
+          <t>2026-08-17 06:33:44</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>178470</v>
+        <v>136722</v>
       </c>
       <c r="G17" t="n">
-        <v>4445</v>
+        <v>2318</v>
       </c>
       <c r="H17" t="n">
-        <v>2027</v>
+        <v>763</v>
       </c>
       <c r="I17" t="n">
-        <v>3316</v>
+        <v>1654</v>
       </c>
       <c r="J17" t="n">
-        <v>377</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="L17" t="n">
-        <v>274</v>
+        <v>35</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
+          <t>61strawberry</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-14 13:49:20</t>
+          <t>2026-08-17 06:33:44</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>142802</v>
+        <v>136740</v>
       </c>
       <c r="G18" t="n">
-        <v>3033</v>
+        <v>2318</v>
       </c>
       <c r="H18" t="n">
-        <v>1053</v>
+        <v>763</v>
       </c>
       <c r="I18" t="n">
-        <v>2025</v>
+        <v>1654</v>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="K18" t="n">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="L18" t="n">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
+          <t>61strawberry</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-14 13:49:20</t>
+          <t>2026-08-17 06:33:44</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>142818</v>
+        <v>136756</v>
       </c>
       <c r="G19" t="n">
-        <v>3033</v>
+        <v>2319</v>
       </c>
       <c r="H19" t="n">
-        <v>1053</v>
+        <v>763</v>
       </c>
       <c r="I19" t="n">
-        <v>2025</v>
+        <v>1654</v>
       </c>
       <c r="J19" t="n">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="K19" t="n">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="L19" t="n">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -5084,44 +5084,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>游园会_杨博文</t>
+          <t>LOST_杨博文</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-14 01:43:31</t>
+          <t>2026-08-13 23:03:07</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>385666</v>
+        <v>436602</v>
       </c>
       <c r="G20" t="n">
-        <v>8279</v>
+        <v>9953</v>
       </c>
       <c r="H20" t="n">
-        <v>3225</v>
+        <v>2657</v>
       </c>
       <c r="I20" t="n">
-        <v>5604</v>
+        <v>7451</v>
       </c>
       <c r="J20" t="n">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="K20" t="n">
-        <v>1759</v>
+        <v>1666</v>
       </c>
       <c r="L20" t="n">
-        <v>1231</v>
+        <v>773</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -5138,266 +5138,266 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>游园会_杨博文</t>
+          <t>LOST_杨博文</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-14 01:43:31</t>
+          <t>2026-08-13 23:03:07</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>385978</v>
+        <v>436907</v>
       </c>
       <c r="G21" t="n">
-        <v>8280</v>
+        <v>9956</v>
       </c>
       <c r="H21" t="n">
-        <v>3225</v>
+        <v>2659</v>
       </c>
       <c r="I21" t="n">
-        <v>5607</v>
+        <v>7455</v>
       </c>
       <c r="J21" t="n">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="K21" t="n">
-        <v>1759</v>
+        <v>1666</v>
       </c>
       <c r="L21" t="n">
-        <v>1232</v>
+        <v>774</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1xwYQ6zEcC</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>红色防吞2</t>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>LOST_杨博文</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:43:19</t>
+          <t>2026-08-13 23:03:07</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13600</v>
+        <v>437216</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>9956</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2659</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>7455</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>894</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1666</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1xwYQ6zEcC</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>红色防吞2</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>我要在森林里盖房子</t>
+          <t>关键时刻来瓶尖叫</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:43:19</t>
+          <t>2026-08-14 01:41:46</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13603</v>
+        <v>178375</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>4444</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2027</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3316</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>377</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>关键时刻来瓶尖叫</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-13 20:48:29</t>
+          <t>2026-08-14 01:41:46</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37911</v>
+        <v>178470</v>
       </c>
       <c r="G24" t="n">
-        <v>12208</v>
+        <v>4445</v>
       </c>
       <c r="H24" t="n">
-        <v>11210</v>
+        <v>2027</v>
       </c>
       <c r="I24" t="n">
-        <v>7617</v>
+        <v>3316</v>
       </c>
       <c r="J24" t="n">
-        <v>4447</v>
+        <v>377</v>
       </c>
       <c r="K24" t="n">
-        <v>483</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>关键时刻来瓶尖叫</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-13 20:48:29</t>
+          <t>2026-08-14 01:41:46</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>37912</v>
+        <v>178585</v>
       </c>
       <c r="G25" t="n">
-        <v>12209</v>
+        <v>4446</v>
       </c>
       <c r="H25" t="n">
-        <v>11212</v>
+        <v>2029</v>
       </c>
       <c r="I25" t="n">
-        <v>7617</v>
+        <v>3316</v>
       </c>
       <c r="J25" t="n">
-        <v>4447</v>
+        <v>377</v>
       </c>
       <c r="K25" t="n">
-        <v>483</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
@@ -5408,44 +5408,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1erbv6AEeL</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Astra_杨博文</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-18 00:34:17</t>
+          <t>2026-08-14 13:49:20</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>161498</v>
+        <v>142802</v>
       </c>
       <c r="G26" t="n">
-        <v>11782</v>
+        <v>3033</v>
       </c>
       <c r="H26" t="n">
-        <v>8702</v>
+        <v>1053</v>
       </c>
       <c r="I26" t="n">
-        <v>11939</v>
+        <v>2025</v>
       </c>
       <c r="J26" t="n">
-        <v>1007</v>
+        <v>356</v>
       </c>
       <c r="K26" t="n">
-        <v>1206</v>
+        <v>225</v>
       </c>
       <c r="L26" t="n">
-        <v>4191</v>
+        <v>102</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -5462,266 +5462,266 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1erbv6AEeL</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Astra_杨博文</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-18 00:34:17</t>
+          <t>2026-08-14 13:49:20</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>161502</v>
+        <v>142818</v>
       </c>
       <c r="G27" t="n">
-        <v>11783</v>
+        <v>3033</v>
       </c>
       <c r="H27" t="n">
-        <v>8702</v>
+        <v>1053</v>
       </c>
       <c r="I27" t="n">
-        <v>11939</v>
+        <v>2025</v>
       </c>
       <c r="J27" t="n">
-        <v>1007</v>
+        <v>356</v>
       </c>
       <c r="K27" t="n">
-        <v>1206</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>4191</v>
+        <v>102</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1WhgW6iEg4</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>序言丨张桂源</t>
+          <t>Astra_杨博文</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-14 00:50:50</t>
+          <t>2026-08-14 13:49:20</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>141754</v>
+        <v>142834</v>
       </c>
       <c r="G28" t="n">
-        <v>7525</v>
+        <v>3033</v>
       </c>
       <c r="H28" t="n">
-        <v>5453</v>
+        <v>1053</v>
       </c>
       <c r="I28" t="n">
-        <v>5614</v>
+        <v>2025</v>
       </c>
       <c r="J28" t="n">
-        <v>424</v>
+        <v>356</v>
       </c>
       <c r="K28" t="n">
-        <v>512</v>
+        <v>225</v>
       </c>
       <c r="L28" t="n">
-        <v>2284</v>
+        <v>102</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1WhgW6iEg4</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>序言丨张桂源</t>
+          <t>游园会_杨博文</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-14 00:50:50</t>
+          <t>2026-08-14 01:43:31</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>141757</v>
+        <v>385666</v>
       </c>
       <c r="G29" t="n">
-        <v>7526</v>
+        <v>8279</v>
       </c>
       <c r="H29" t="n">
-        <v>5453</v>
+        <v>3225</v>
       </c>
       <c r="I29" t="n">
-        <v>5614</v>
+        <v>5604</v>
       </c>
       <c r="J29" t="n">
-        <v>424</v>
+        <v>888</v>
       </c>
       <c r="K29" t="n">
-        <v>512</v>
+        <v>1759</v>
       </c>
       <c r="L29" t="n">
-        <v>2284</v>
+        <v>1231</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1vdbC6RE8S</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Euphoria欢欣丨张桂源</t>
+          <t>游园会_杨博文</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:48</t>
+          <t>2026-08-14 01:43:31</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>106282</v>
+        <v>385978</v>
       </c>
       <c r="G30" t="n">
-        <v>9774</v>
+        <v>8280</v>
       </c>
       <c r="H30" t="n">
-        <v>9801</v>
+        <v>3225</v>
       </c>
       <c r="I30" t="n">
-        <v>10347</v>
+        <v>5607</v>
       </c>
       <c r="J30" t="n">
-        <v>932</v>
+        <v>889</v>
       </c>
       <c r="K30" t="n">
-        <v>1214</v>
+        <v>1759</v>
       </c>
       <c r="L30" t="n">
-        <v>3772</v>
+        <v>1232</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1vdbC6RE8S</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Euphoria欢欣丨张桂源</t>
+          <t>游园会_杨博文</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:48</t>
+          <t>2026-08-14 01:43:31</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>106282</v>
+        <v>386301</v>
       </c>
       <c r="G31" t="n">
-        <v>9774</v>
+        <v>8281</v>
       </c>
       <c r="H31" t="n">
-        <v>9801</v>
+        <v>3227</v>
       </c>
       <c r="I31" t="n">
-        <v>10347</v>
+        <v>5608</v>
       </c>
       <c r="J31" t="n">
-        <v>932</v>
+        <v>889</v>
       </c>
       <c r="K31" t="n">
-        <v>1214</v>
+        <v>1759</v>
       </c>
       <c r="L31" t="n">
-        <v>3772</v>
+        <v>1232</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
@@ -5732,44 +5732,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1C8gW6KEkX</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-14 00:43:15</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>208266</v>
+        <v>37911</v>
       </c>
       <c r="G32" t="n">
-        <v>8985</v>
+        <v>12208</v>
       </c>
       <c r="H32" t="n">
-        <v>4793</v>
+        <v>11210</v>
       </c>
       <c r="I32" t="n">
-        <v>6808</v>
+        <v>7617</v>
       </c>
       <c r="J32" t="n">
-        <v>447</v>
+        <v>4447</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L32" t="n">
-        <v>9316</v>
+        <v>21</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -5786,98 +5786,98 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1C8gW6KEkX</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Split0511-张桂源</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-14 00:43:15</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>208268</v>
+        <v>37912</v>
       </c>
       <c r="G33" t="n">
-        <v>8985</v>
+        <v>12209</v>
       </c>
       <c r="H33" t="n">
-        <v>4793</v>
+        <v>11212</v>
       </c>
       <c r="I33" t="n">
-        <v>6808</v>
+        <v>7617</v>
       </c>
       <c r="J33" t="n">
-        <v>447</v>
+        <v>4447</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L33" t="n">
-        <v>9316</v>
+        <v>21</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1qiBkBGEoj</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>wish0511_张桂源</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-12-27 16:42:34</t>
+          <t>2026-08-13 20:48:29</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>980762</v>
+        <v>37912</v>
       </c>
       <c r="G34" t="n">
-        <v>16726</v>
+        <v>12209</v>
       </c>
       <c r="H34" t="n">
-        <v>11033</v>
+        <v>11212</v>
       </c>
       <c r="I34" t="n">
-        <v>14544</v>
+        <v>7617</v>
       </c>
       <c r="J34" t="n">
-        <v>1299</v>
+        <v>4447</v>
       </c>
       <c r="K34" t="n">
-        <v>1437</v>
+        <v>483</v>
       </c>
       <c r="L34" t="n">
-        <v>4834</v>
+        <v>21</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5889,61 +5889,61 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 00:30:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1qiBkBGEoj</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+          <t>红色防吞3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wish0511_张桂源</t>
+          <t>我要在森林里盖房子</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-12-27 16:42:34</t>
+          <t>2026-09-15 01:28:46</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>980765</v>
+        <v>11050</v>
       </c>
       <c r="G35" t="n">
-        <v>16726</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>11033</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>14545</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>1299</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>4834</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 00:30:00</t>
+          <t>2026-09-18 01:00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11050</v>
+        <v>11131</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
@@ -5976,7 +5976,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>12</v>
@@ -5991,13 +5991,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 01:00:00</t>
+          <t>2026-09-18 01:30:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11131</v>
+        <v>11218</v>
       </c>
       <c r="G37" t="n">
         <v>4</v>
@@ -6045,7 +6045,655 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>81</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BV1xwYQ6zEcC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>红色防吞2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:43:19</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>13600</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BV1xwYQ6zEcC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>红色防吞2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:43:19</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>13603</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BV1erbv6AEeL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>【张桂源】 刺 4k 横版focus</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-08-18 00:34:17</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>161498</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11782</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8702</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11939</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1007</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4191</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BV1erbv6AEeL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>【张桂源】 刺 4k 横版focus</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-08-18 00:34:17</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>161502</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11783</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8702</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11939</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1007</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4191</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BV1WhgW6iEg4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>序言丨张桂源</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:50:50</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>141754</v>
+      </c>
+      <c r="G42" t="n">
+        <v>7525</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5453</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5614</v>
+      </c>
+      <c r="J42" t="n">
+        <v>424</v>
+      </c>
+      <c r="K42" t="n">
+        <v>512</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2284</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BV1WhgW6iEg4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>序言丨张桂源</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:50:50</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>141757</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7526</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5453</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5614</v>
+      </c>
+      <c r="J43" t="n">
+        <v>424</v>
+      </c>
+      <c r="K43" t="n">
+        <v>512</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2284</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BV1vdbC6RE8S</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Euphoria欢欣丨张桂源</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:00:48</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>106282</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9774</v>
+      </c>
+      <c r="H44" t="n">
+        <v>9801</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10347</v>
+      </c>
+      <c r="J44" t="n">
+        <v>932</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3772</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BV1vdbC6RE8S</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Euphoria欢欣丨张桂源</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:00:48</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>106282</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9774</v>
+      </c>
+      <c r="H45" t="n">
+        <v>9801</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10347</v>
+      </c>
+      <c r="J45" t="n">
+        <v>932</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3772</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BV1C8gW6KEkX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:43:15</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>208266</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8985</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4793</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6808</v>
+      </c>
+      <c r="J46" t="n">
+        <v>447</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9316</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV1C8gW6KEkX</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:43:15</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>208268</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8985</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4793</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6808</v>
+      </c>
+      <c r="J47" t="n">
+        <v>447</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9316</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:30:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BV1qiBkBGEoj</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>wish0511_张桂源</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-12-27 16:42:34</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>980762</v>
+      </c>
+      <c r="G48" t="n">
+        <v>16726</v>
+      </c>
+      <c r="H48" t="n">
+        <v>11033</v>
+      </c>
+      <c r="I48" t="n">
+        <v>14544</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1299</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4834</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BV1qiBkBGEoj</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>wish0511_张桂源</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-12-27 16:42:34</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>980765</v>
+      </c>
+      <c r="G49" t="n">
+        <v>16726</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11033</v>
+      </c>
+      <c r="I49" t="n">
+        <v>14545</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1299</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4834</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6103,10 +6751,10 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-360,179 -&gt; 360,199
-▲ +20 (+0.0%)
+360,179 -&gt; 360,215
+▲ +36 (+0.0%)
 ▶ 点赞
 30,865 -&gt; 30,865
 ▲ +0 (+0.0%)
@@ -6114,8 +6762,8 @@
 23,642 -&gt; 23,642
 ▲ +0 (+0.0%)
 ▶ 收藏
-23,320 -&gt; 23,320
-▲ +0 (+0.0%)
+23,320 -&gt; 23,321
+▲ +1 (+0.0%)
 ▶ 转发
 7,168 -&gt; 7,168
 ▲ +0 (+0.0%)
@@ -6147,19 +6795,19 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-339,040 -&gt; 339,129
-▲ +89 (+0.0%)
+339,040 -&gt; 339,229
+▲ +189 (+0.1%)
 ▶ 点赞
-26,695 -&gt; 26,697
+26,695 -&gt; 26,700
+▲ +5 (+0.0%)
+▶ 投币
+16,876 -&gt; 16,880
+▲ +4 (+0.0%)
+▶ 收藏
+19,119 -&gt; 19,121
 ▲ +2 (+0.0%)
-▶ 投币
-16,876 -&gt; 16,878
-▲ +2 (+0.0%)
-▶ 收藏
-19,119 -&gt; 19,120
-▲ +1 (+0.0%)
 ▶ 转发
 6,422 -&gt; 6,422
 ▲ +0 (+0.0%)
@@ -6191,19 +6839,19 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-371,396 -&gt; 371,486
-▲ +90 (+0.0%)
+371,396 -&gt; 371,580
+▲ +184 (+0.0%)
 ▶ 点赞
-21,259 -&gt; 21,262
-▲ +3 (+0.0%)
+21,259 -&gt; 21,263
+▲ +4 (+0.0%)
 ▶ 投币
-12,230 -&gt; 12,232
+12,230 -&gt; 12,236
+▲ +6 (+0.0%)
+▶ 收藏
+17,509 -&gt; 17,511
 ▲ +2 (+0.0%)
-▶ 收藏
-17,509 -&gt; 17,510
-▲ +1 (+0.0%)
 ▶ 转发
 3,425 -&gt; 3,425
 ▲ +0 (+0.0%)
@@ -6235,25 +6883,25 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-472,541 -&gt; 472,642
-▲ +101 (+0.0%)
+472,541 -&gt; 472,753
+▲ +212 (+0.0%)
 ▶ 点赞
-38,141 -&gt; 38,141
-▲ +0 (+0.0%)
+38,141 -&gt; 38,143
+▲ +2 (+0.0%)
 ▶ 投币
 17,267 -&gt; 17,267
 ▲ +0 (+0.0%)
 ▶ 收藏
-25,701 -&gt; 25,704
-▲ +3 (+0.0%)
+25,701 -&gt; 25,705
+▲ +4 (+0.0%)
 ▶ 转发
 6,212 -&gt; 6,213
 ▲ +1 (+0.0%)
 ▶ 评论
-12,622 -&gt; 12,622
-▲ +0 (+0.0%)
+12,622 -&gt; 12,623
+▲ +1 (+0.0%)
 ▶ 弹幕
 14,938 -&gt; 14,938
 ▲ +0 (+0.0%)</t>
@@ -6279,16 +6927,16 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-334,571 -&gt; 334,864
-▲ +293 (+0.1%)
+334,571 -&gt; 335,169
+▲ +598 (+0.2%)
 ▶ 点赞
-5,745 -&gt; 5,746
-▲ +1 (+0.0%)
+5,745 -&gt; 5,749
+▲ +4 (+0.1%)
 ▶ 投币
-2,924 -&gt; 2,924
-▲ +0 (+0.0%)
+2,924 -&gt; 2,926
+▲ +2 (+0.1%)
 ▶ 收藏
 3,460 -&gt; 3,462
 ▲ +2 (+0.1%)
@@ -6323,13 +6971,13 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-136,722 -&gt; 136,740
-▲ +18 (+0.0%)
+136,722 -&gt; 136,756
+▲ +34 (+0.0%)
 ▶ 点赞
-2,318 -&gt; 2,318
-▲ +0 (+0.0%)
+2,318 -&gt; 2,319
+▲ +1 (+0.0%)
 ▶ 投币
 763 -&gt; 763
 ▲ +0 (+0.0%)
@@ -6367,10 +7015,10 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-436,602 -&gt; 436,907
-▲ +305 (+0.1%)
+436,602 -&gt; 437,216
+▲ +614 (+0.1%)
 ▶ 点赞
 9,953 -&gt; 9,956
 ▲ +3 (+0.0%)
@@ -6411,16 +7059,16 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-178,375 -&gt; 178,470
-▲ +95 (+0.1%)
+178,375 -&gt; 178,585
+▲ +210 (+0.1%)
 ▶ 点赞
-4,444 -&gt; 4,445
-▲ +1 (+0.0%)
+4,444 -&gt; 4,446
+▲ +2 (+0.0%)
 ▶ 投币
-2,027 -&gt; 2,027
-▲ +0 (+0.0%)
+2,027 -&gt; 2,029
+▲ +2 (+0.1%)
 ▶ 收藏
 3,316 -&gt; 3,316
 ▲ +0 (+0.0%)
@@ -6455,10 +7103,10 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-142,802 -&gt; 142,818
-▲ +16 (+0.0%)
+142,802 -&gt; 142,834
+▲ +32 (+0.0%)
 ▶ 点赞
 3,033 -&gt; 3,033
 ▲ +0 (+0.0%)
@@ -6499,19 +7147,19 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
-截至 09月18日 01:00
+截至 09月18日 01:30
 ▶ 播放量
-385,666 -&gt; 385,978
-▲ +312 (+0.1%)
+385,666 -&gt; 386,301
+▲ +635 (+0.2%)
 ▶ 点赞
-8,279 -&gt; 8,280
-▲ +1 (+0.0%)
+8,279 -&gt; 8,281
+▲ +2 (+0.0%)
 ▶ 投币
-3,225 -&gt; 3,225
-▲ +0 (+0.0%)
+3,225 -&gt; 3,227
+▲ +2 (+0.1%)
 ▶ 收藏
-5,604 -&gt; 5,607
-▲ +3 (+0.1%)
+5,604 -&gt; 5,608
+▲ +4 (+0.1%)
 ▶ 转发
 888 -&gt; 889
 ▲ +1 (+0.1%)
@@ -6527,20 +7175,328 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:30
+▶ 播放量
+37,911 -&gt; 37,912
+▲ +1 (+0.0%)
+▶ 点赞
+12,208 -&gt; 12,209
+▲ +1 (+0.0%)
+▶ 投币
+11,210 -&gt; 11,212
+▲ +2 (+0.0%)
+▶ 收藏
+7,617 -&gt; 7,617
+▲ +0 (+0.0%)
+▶ 转发
+4,447 -&gt; 4,447
+▲ +0 (+0.0%)
+▶ 评论
+483 -&gt; 483
+▲ +0 (+0.0%)
+▶ 弹幕
+21 -&gt; 21
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:30
+▶ 播放量
+11,050 -&gt; 11,218
+▲ +168 (+1.5%)
+▶ 点赞
+4 -&gt; 4
+▲ +0 (+0.0%)
+▶ 投币
+6 -&gt; 6
+▲ +0 (+0.0%)
+▶ 收藏
+7 -&gt; 6
+▼ -1 (-14.3%)
+▶ 转发
+12 -&gt; 12
+▲ +0 (+0.0%)
+▶ 评论
+0 -&gt; 0
+▲ +0 (+0.0%)
+▶ 弹幕
+0 -&gt; 0
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BV1C8gW6KEkX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:00
+▶ 播放量
+208,266 -&gt; 208,268
+▲ +2 (+0.0%)
+▶ 点赞
+8,985 -&gt; 8,985
+▲ +0 (+0.0%)
+▶ 投币
+4,793 -&gt; 4,793
+▲ +0 (+0.0%)
+▶ 收藏
+6,808 -&gt; 6,808
+▲ +0 (+0.0%)
+▶ 转发
+447 -&gt; 447
+▲ +0 (+0.0%)
+▶ 评论
+0 -&gt; 0
+▲ +0 (+0.0%)
+▶ 弹幕
+9,316 -&gt; 9,316
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BV1WhgW6iEg4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>序言丨张桂源</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:00
+▶ 播放量
+141,754 -&gt; 141,757
+▲ +3 (+0.0%)
+▶ 点赞
+7,525 -&gt; 7,526
+▲ +1 (+0.0%)
+▶ 投币
+5,453 -&gt; 5,453
+▲ +0 (+0.0%)
+▶ 收藏
+5,614 -&gt; 5,614
+▲ +0 (+0.0%)
+▶ 转发
+424 -&gt; 424
+▲ +0 (+0.0%)
+▶ 评论
+512 -&gt; 512
+▲ +0 (+0.0%)
+▶ 弹幕
+2,284 -&gt; 2,284
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BV1erbv6AEeL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Split0511-张桂源</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>【张桂源】 刺 4k 横版focus</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:00
+▶ 播放量
+161,498 -&gt; 161,502
+▲ +4 (+0.0%)
+▶ 点赞
+11,782 -&gt; 11,783
+▲ +1 (+0.0%)
+▶ 投币
+8,702 -&gt; 8,702
+▲ +0 (+0.0%)
+▶ 收藏
+11,939 -&gt; 11,939
+▲ +0 (+0.0%)
+▶ 转发
+1,007 -&gt; 1,007
+▲ +0 (+0.0%)
+▶ 评论
+1,206 -&gt; 1,206
+▲ +0 (+0.0%)
+▶ 弹幕
+4,191 -&gt; 4,191
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BV1qiBkBGEoj</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>wish0511_张桂源</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:00
+▶ 播放量
+980,762 -&gt; 980,765
+▲ +3 (+0.0%)
+▶ 点赞
+16,726 -&gt; 16,726
+▲ +0 (+0.0%)
+▶ 投币
+11,033 -&gt; 11,033
+▲ +0 (+0.0%)
+▶ 收藏
+14,544 -&gt; 14,545
+▲ +1 (+0.0%)
+▶ 转发
+1,299 -&gt; 1,299
+▲ +0 (+0.0%)
+▶ 评论
+1,437 -&gt; 1,437
+▲ +0 (+0.0%)
+▶ 弹幕
+4,834 -&gt; 4,834
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BV1vdbC6RE8S</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Euphoria欢欣丨张桂源</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>📈 【今日数据播报】
+截至 09月18日 01:00
+▶ 播放量
+106,282 -&gt; 106,282
+▲ +0 (+0.0%)
+▶ 点赞
+9,774 -&gt; 9,774
+▲ +0 (+0.0%)
+▶ 投币
+9,801 -&gt; 9,801
+▲ +0 (+0.0%)
+▶ 收藏
+10,347 -&gt; 10,347
+▲ +0 (+0.0%)
+▶ 转发
+932 -&gt; 932
+▲ +0 (+0.0%)
+▶ 评论
+1,214 -&gt; 1,214
+▲ +0 (+0.0%)
+▶ 弹幕
+3,772 -&gt; 3,772
+▲ +0 (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>BV1xwYQ6zEcC</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>我要在森林里盖房子</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>红色防吞2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>📈 【今日数据播报】
 截至 09月18日 01:00
@@ -6568,314 +7524,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BV18ZgH6uEYv</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Roseate丨杨博文</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-37,911 -&gt; 37,912
-▲ +1 (+0.0%)
-▶ 点赞
-12,208 -&gt; 12,209
-▲ +1 (+0.0%)
-▶ 投币
-11,210 -&gt; 11,212
-▲ +2 (+0.0%)
-▶ 收藏
-7,617 -&gt; 7,617
-▲ +0 (+0.0%)
-▶ 转发
-4,447 -&gt; 4,447
-▲ +0 (+0.0%)
-▶ 评论
-483 -&gt; 483
-▲ +0 (+0.0%)
-▶ 弹幕
-21 -&gt; 21
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BV1erbv6AEeL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Split0511-张桂源</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>【张桂源】 刺 4k 横版focus</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-161,498 -&gt; 161,502
-▲ +4 (+0.0%)
-▶ 点赞
-11,782 -&gt; 11,783
-▲ +1 (+0.0%)
-▶ 投币
-8,702 -&gt; 8,702
-▲ +0 (+0.0%)
-▶ 收藏
-11,939 -&gt; 11,939
-▲ +0 (+0.0%)
-▶ 转发
-1,007 -&gt; 1,007
-▲ +0 (+0.0%)
-▶ 评论
-1,206 -&gt; 1,206
-▲ +0 (+0.0%)
-▶ 弹幕
-4,191 -&gt; 4,191
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BV1WhgW6iEg4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>序言丨张桂源</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>「100ways」张桂源直拍 烧烧的好会扭</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-141,754 -&gt; 141,757
-▲ +3 (+0.0%)
-▶ 点赞
-7,525 -&gt; 7,526
-▲ +1 (+0.0%)
-▶ 投币
-5,453 -&gt; 5,453
-▲ +0 (+0.0%)
-▶ 收藏
-5,614 -&gt; 5,614
-▲ +0 (+0.0%)
-▶ 转发
-424 -&gt; 424
-▲ +0 (+0.0%)
-▶ 评论
-512 -&gt; 512
-▲ +0 (+0.0%)
-▶ 弹幕
-2,284 -&gt; 2,284
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BV1vdbC6RE8S</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Euphoria欢欣丨张桂源</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>【4K直拍｜张桂源】Whiplash四机位｜第肆象限20260813&amp;0814</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-106,282 -&gt; 106,282
-▲ +0 (+0.0%)
-▶ 点赞
-9,774 -&gt; 9,774
-▲ +0 (+0.0%)
-▶ 投币
-9,801 -&gt; 9,801
-▲ +0 (+0.0%)
-▶ 收藏
-10,347 -&gt; 10,347
-▲ +0 (+0.0%)
-▶ 转发
-932 -&gt; 932
-▲ +0 (+0.0%)
-▶ 评论
-1,214 -&gt; 1,214
-▲ +0 (+0.0%)
-▶ 弹幕
-3,772 -&gt; 3,772
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BV1C8gW6KEkX</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Split0511-张桂源</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>【张桂源】 异常加载中 4k focus 横版直拍</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-208,266 -&gt; 208,268
-▲ +2 (+0.0%)
-▶ 点赞
-8,985 -&gt; 8,985
-▲ +0 (+0.0%)
-▶ 投币
-4,793 -&gt; 4,793
-▲ +0 (+0.0%)
-▶ 收藏
-6,808 -&gt; 6,808
-▲ +0 (+0.0%)
-▶ 转发
-447 -&gt; 447
-▲ +0 (+0.0%)
-▶ 评论
-0 -&gt; 0
-▲ +0 (+0.0%)
-▶ 弹幕
-9,316 -&gt; 9,316
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BV1qiBkBGEoj</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>wish0511_张桂源</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>【张桂源】On 4k四机位横屏直拍 / TF家族新年音乐会「荣耀」</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-980,762 -&gt; 980,765
-▲ +3 (+0.0%)
-▶ 点赞
-16,726 -&gt; 16,726
-▲ +0 (+0.0%)
-▶ 投币
-11,033 -&gt; 11,033
-▲ +0 (+0.0%)
-▶ 收藏
-14,544 -&gt; 14,545
-▲ +1 (+0.0%)
-▶ 转发
-1,299 -&gt; 1,299
-▲ +0 (+0.0%)
-▶ 评论
-1,437 -&gt; 1,437
-▲ +0 (+0.0%)
-▶ 弹幕
-4,834 -&gt; 4,834
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BV1r8eV6fE5N</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>我要在森林里盖房子</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>红色防吞3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>📈 【今日数据播报】
-截至 09月18日 01:00
-▶ 播放量
-11,050 -&gt; 11,131
-▲ +81 (+0.7%)
-▶ 点赞
-4 -&gt; 4
-▲ +0 (+0.0%)
-▶ 投币
-6 -&gt; 6
-▲ +0 (+0.0%)
-▶ 收藏
-7 -&gt; 6
-▼ -1 (-14.3%)
-▶ 转发
-12 -&gt; 12
-▲ +0 (+0.0%)
-▶ 评论
-0 -&gt; 0
-▲ +0 (+0.0%)
-▶ 弹幕
-0 -&gt; 0
-▲ +0 (+0.0%)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2680,6 +2680,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:21:40</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>360333</v>
+      </c>
+      <c r="W33" t="n">
+        <v>30868</v>
+      </c>
+      <c r="X33" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:21:44</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>340526</v>
+      </c>
+      <c r="W34" t="n">
+        <v>26711</v>
+      </c>
+      <c r="X34" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19126</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6422</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:21:48</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>372843</v>
+      </c>
+      <c r="W35" t="n">
+        <v>21271</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12240</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17519</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3425</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:21:53</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>474198</v>
+      </c>
+      <c r="W36" t="n">
+        <v>38154</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17274</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>25712</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6223</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>14939</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:21:57</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>339489</v>
+      </c>
+      <c r="W37" t="n">
+        <v>5755</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2930</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3468</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>882</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:01</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>136946</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2321</v>
+      </c>
+      <c r="X38" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:05</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>441747</v>
+      </c>
+      <c r="W39" t="n">
+        <v>9961</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2671</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7460</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>896</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:09</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>180044</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>377</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:13</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>143057</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3036</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1055</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:18</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>390679</v>
+      </c>
+      <c r="W42" t="n">
+        <v>8287</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>5613</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>889</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:22</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>37914</v>
+      </c>
+      <c r="W43" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X43" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:22:26</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>12338</v>
+      </c>
+      <c r="W44" t="n">
+        <v>4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3400,6 +3400,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:35</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>360346</v>
+      </c>
+      <c r="W45" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X45" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:38</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>340605</v>
+      </c>
+      <c r="W46" t="n">
+        <v>26711</v>
+      </c>
+      <c r="X46" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>19126</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>6422</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:43</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>372920</v>
+      </c>
+      <c r="W47" t="n">
+        <v>21272</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12240</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>17519</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3425</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:47</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>474300</v>
+      </c>
+      <c r="W48" t="n">
+        <v>38155</v>
+      </c>
+      <c r="X48" t="n">
+        <v>17274</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>25712</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>6223</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>14940</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:51</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>339751</v>
+      </c>
+      <c r="W49" t="n">
+        <v>5756</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2932</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3469</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>882</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:55</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>136954</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2321</v>
+      </c>
+      <c r="X50" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:45:59</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>442013</v>
+      </c>
+      <c r="W51" t="n">
+        <v>9963</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2672</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>7461</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>896</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:46:03</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>180115</v>
+      </c>
+      <c r="W52" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>377</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:46:07</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>143070</v>
+      </c>
+      <c r="W53" t="n">
+        <v>3036</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:46:11</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>390953</v>
+      </c>
+      <c r="W54" t="n">
+        <v>8287</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>5613</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>889</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:46:15</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>37915</v>
+      </c>
+      <c r="W55" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X55" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:46:19</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>12396</v>
+      </c>
+      <c r="W56" t="n">
+        <v>4</v>
+      </c>
+      <c r="X56" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AB68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4120,6 +4120,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:19</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>360359</v>
+      </c>
+      <c r="W57" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X57" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:23</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>340719</v>
+      </c>
+      <c r="W58" t="n">
+        <v>26711</v>
+      </c>
+      <c r="X58" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>19126</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>6422</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:27</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>373028</v>
+      </c>
+      <c r="W59" t="n">
+        <v>21273</v>
+      </c>
+      <c r="X59" t="n">
+        <v>12240</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>17519</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>3425</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:32</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>474466</v>
+      </c>
+      <c r="W60" t="n">
+        <v>38162</v>
+      </c>
+      <c r="X60" t="n">
+        <v>17276</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>25715</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>6223</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>14940</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:36</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>340141</v>
+      </c>
+      <c r="W61" t="n">
+        <v>5756</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2932</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>3470</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>882</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:40</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>136966</v>
+      </c>
+      <c r="W62" t="n">
+        <v>2322</v>
+      </c>
+      <c r="X62" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:45</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>442382</v>
+      </c>
+      <c r="W63" t="n">
+        <v>9963</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2672</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7461</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>896</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:49</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>180227</v>
+      </c>
+      <c r="W64" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>377</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:53</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>143087</v>
+      </c>
+      <c r="W65" t="n">
+        <v>3037</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:19:58</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>391330</v>
+      </c>
+      <c r="W66" t="n">
+        <v>8288</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>5614</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>889</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:20:02</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>37915</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X67" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:20:06</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>12483</v>
+      </c>
+      <c r="W68" t="n">
+        <v>4</v>
+      </c>
+      <c r="X68" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AB80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4840,6 +4840,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:45:44</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>360367</v>
+      </c>
+      <c r="W69" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X69" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:45:48</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>340811</v>
+      </c>
+      <c r="W70" t="n">
+        <v>26711</v>
+      </c>
+      <c r="X70" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>19125</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>6422</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:45:52</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>373112</v>
+      </c>
+      <c r="W71" t="n">
+        <v>21274</v>
+      </c>
+      <c r="X71" t="n">
+        <v>12240</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>17521</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>3425</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:45:56</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>474597</v>
+      </c>
+      <c r="W72" t="n">
+        <v>38163</v>
+      </c>
+      <c r="X72" t="n">
+        <v>17276</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>25716</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>6223</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>14940</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:00</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>340446</v>
+      </c>
+      <c r="W73" t="n">
+        <v>5759</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2934</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>3470</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>882</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:04</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>136975</v>
+      </c>
+      <c r="W74" t="n">
+        <v>2322</v>
+      </c>
+      <c r="X74" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:09</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>442666</v>
+      </c>
+      <c r="W75" t="n">
+        <v>9963</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2672</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7461</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>896</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:13</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>180313</v>
+      </c>
+      <c r="W76" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>377</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:17</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>143100</v>
+      </c>
+      <c r="W77" t="n">
+        <v>3037</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:21</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>391637</v>
+      </c>
+      <c r="W78" t="n">
+        <v>8288</v>
+      </c>
+      <c r="X78" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>5614</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>889</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:25</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>37915</v>
+      </c>
+      <c r="W79" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X79" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:46:29</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>12558</v>
+      </c>
+      <c r="W80" t="n">
+        <v>4</v>
+      </c>
+      <c r="X80" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB80"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5560,6 +5560,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:19:43</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>360387</v>
+      </c>
+      <c r="W81" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X81" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:19:47</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>340921</v>
+      </c>
+      <c r="W82" t="n">
+        <v>26713</v>
+      </c>
+      <c r="X82" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>19126</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>6424</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:19:51</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>373229</v>
+      </c>
+      <c r="W83" t="n">
+        <v>21275</v>
+      </c>
+      <c r="X83" t="n">
+        <v>12240</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>17521</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>3427</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:19:55</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>474758</v>
+      </c>
+      <c r="W84" t="n">
+        <v>38165</v>
+      </c>
+      <c r="X84" t="n">
+        <v>17276</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>25719</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>6225</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>14940</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:19:59</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>340808</v>
+      </c>
+      <c r="W85" t="n">
+        <v>5759</v>
+      </c>
+      <c r="X85" t="n">
+        <v>2934</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>3470</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>884</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:03</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>136988</v>
+      </c>
+      <c r="W86" t="n">
+        <v>2322</v>
+      </c>
+      <c r="X86" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:07</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>443034</v>
+      </c>
+      <c r="W87" t="n">
+        <v>9963</v>
+      </c>
+      <c r="X87" t="n">
+        <v>2672</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>7461</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>898</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:11</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>180428</v>
+      </c>
+      <c r="W88" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X88" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>379</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:16</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>143118</v>
+      </c>
+      <c r="W89" t="n">
+        <v>3037</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:20</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>392019</v>
+      </c>
+      <c r="W90" t="n">
+        <v>8289</v>
+      </c>
+      <c r="X90" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>5614</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>891</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:24</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>37915</v>
+      </c>
+      <c r="W91" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X91" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:20:28</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>12650</v>
+      </c>
+      <c r="W92" t="n">
+        <v>5</v>
+      </c>
+      <c r="X92" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB92"/>
+  <dimension ref="A1:AB104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6280,6 +6280,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:34</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>360397</v>
+      </c>
+      <c r="W93" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X93" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>23323</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:38</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V94" t="n">
+        <v>341019</v>
+      </c>
+      <c r="W94" t="n">
+        <v>26714</v>
+      </c>
+      <c r="X94" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>19127</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>6424</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:43</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>373328</v>
+      </c>
+      <c r="W95" t="n">
+        <v>21277</v>
+      </c>
+      <c r="X95" t="n">
+        <v>12242</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>17525</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>3427</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:47</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>474888</v>
+      </c>
+      <c r="W96" t="n">
+        <v>38167</v>
+      </c>
+      <c r="X96" t="n">
+        <v>17276</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>25721</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>6225</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>14941</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:51</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>341100</v>
+      </c>
+      <c r="W97" t="n">
+        <v>5760</v>
+      </c>
+      <c r="X97" t="n">
+        <v>2934</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>3470</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>884</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>2101</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:45:55</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>137000</v>
+      </c>
+      <c r="W98" t="n">
+        <v>2323</v>
+      </c>
+      <c r="X98" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1656</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:00</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>443348</v>
+      </c>
+      <c r="W99" t="n">
+        <v>9964</v>
+      </c>
+      <c r="X99" t="n">
+        <v>2672</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>7462</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>898</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:04</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>180519</v>
+      </c>
+      <c r="W100" t="n">
+        <v>4447</v>
+      </c>
+      <c r="X100" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>3316</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>379</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:08</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V101" t="n">
+        <v>143130</v>
+      </c>
+      <c r="W101" t="n">
+        <v>3038</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:13</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V102" t="n">
+        <v>392316</v>
+      </c>
+      <c r="W102" t="n">
+        <v>8291</v>
+      </c>
+      <c r="X102" t="n">
+        <v>3231</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>5616</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>891</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>1759</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:17</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>37916</v>
+      </c>
+      <c r="W103" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X103" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:46:21</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>12725</v>
+      </c>
+      <c r="W104" t="n">
+        <v>5</v>
+      </c>
+      <c r="X104" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB104"/>
+  <dimension ref="A1:AB116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7000,6 +7000,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:18:42</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>360414</v>
+      </c>
+      <c r="W105" t="n">
+        <v>30870</v>
+      </c>
+      <c r="X105" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>23322</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:18:47</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V106" t="n">
+        <v>341180</v>
+      </c>
+      <c r="W106" t="n">
+        <v>26715</v>
+      </c>
+      <c r="X106" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>19128</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>6424</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>7612</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:18:51</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V107" t="n">
+        <v>373504</v>
+      </c>
+      <c r="W107" t="n">
+        <v>21280</v>
+      </c>
+      <c r="X107" t="n">
+        <v>12244</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>17526</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>3427</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:18:55</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V108" t="n">
+        <v>475099</v>
+      </c>
+      <c r="W108" t="n">
+        <v>38172</v>
+      </c>
+      <c r="X108" t="n">
+        <v>17278</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>25729</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>6226</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>12623</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>14941</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:18:59</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V109" t="n">
+        <v>341486</v>
+      </c>
+      <c r="W109" t="n">
+        <v>5766</v>
+      </c>
+      <c r="X109" t="n">
+        <v>2938</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>3474</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>885</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>2111</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:04</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V110" t="n">
+        <v>137020</v>
+      </c>
+      <c r="W110" t="n">
+        <v>2324</v>
+      </c>
+      <c r="X110" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1658</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:08</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V111" t="n">
+        <v>443728</v>
+      </c>
+      <c r="W111" t="n">
+        <v>9964</v>
+      </c>
+      <c r="X111" t="n">
+        <v>2673</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>7462</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>898</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>1666</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:13</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>180654</v>
+      </c>
+      <c r="W112" t="n">
+        <v>4448</v>
+      </c>
+      <c r="X112" t="n">
+        <v>2032</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>3318</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>379</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:17</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>143157</v>
+      </c>
+      <c r="W113" t="n">
+        <v>3039</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1057</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>2030</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:21</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V114" t="n">
+        <v>392695</v>
+      </c>
+      <c r="W114" t="n">
+        <v>8292</v>
+      </c>
+      <c r="X114" t="n">
+        <v>3235</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>5618</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>892</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>1769</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:26</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>37917</v>
+      </c>
+      <c r="W115" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X115" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:19:30</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>12844</v>
+      </c>
+      <c r="W116" t="n">
+        <v>5</v>
+      </c>
+      <c r="X116" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB116"/>
+  <dimension ref="A1:AB128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7720,6 +7720,726 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:06</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>BV1GdgW6JEe9</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】Whiplash直拍合集（双日混剪+单日）</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>360422</v>
+      </c>
+      <c r="W117" t="n">
+        <v>30871</v>
+      </c>
+      <c r="X117" t="n">
+        <v>23644</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>23322</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>5239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:10</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>BV1W5gs6KEhr</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>【4K精剪】异常加载中 | 杨博文直拍 | 四天混剪 | 第肆象限演唱会</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V118" t="n">
+        <v>341282</v>
+      </c>
+      <c r="W118" t="n">
+        <v>26716</v>
+      </c>
+      <c r="X118" t="n">
+        <v>16884</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>19128</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>6424</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>7613</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:15</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>【4K精剪】Attention | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>373615</v>
+      </c>
+      <c r="W119" t="n">
+        <v>21284</v>
+      </c>
+      <c r="X119" t="n">
+        <v>12244</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>17526</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>3427</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:19</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>BV1E2bR6hEJR</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>【杨博文】Attention丨直拍横屏丨16岁高中生内娱主舞的舞台掌控力丨8.16双机位4k精剪</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Kismet丨杨博文</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>475252</v>
+      </c>
+      <c r="W120" t="n">
+        <v>38174</v>
+      </c>
+      <c r="X120" t="n">
+        <v>17278</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>25730</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>6226</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>12624</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>14941</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:23</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>【4K精剪】管他什么音乐 | 杨博文直拍 | 260816</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>underthepoplar</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>341777</v>
+      </c>
+      <c r="W121" t="n">
+        <v>5768</v>
+      </c>
+      <c r="X121" t="n">
+        <v>2940</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>3476</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>885</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>2112</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:27</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>杨博文｜260816第肆象限attention&lt;4k精剪&gt;</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>61strawberry</t>
+        </is>
+      </c>
+      <c r="V122" t="n">
+        <v>137039</v>
+      </c>
+      <c r="W122" t="n">
+        <v>2324</v>
+      </c>
+      <c r="X122" t="n">
+        <v>763</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1658</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:31</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>BV15egs6pEJp</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>杨博文｜Whiplash 2机位精剪 直拍 fancam｜4K60｜260813</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>LOST_杨博文</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>444013</v>
+      </c>
+      <c r="W123" t="n">
+        <v>9964</v>
+      </c>
+      <c r="X123" t="n">
+        <v>2673</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>7462</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>899</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>1676</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:35</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="V124" t="n">
+        <v>180771</v>
+      </c>
+      <c r="W124" t="n">
+        <v>4448</v>
+      </c>
+      <c r="X124" t="n">
+        <v>2032</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>3318</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>379</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:40</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="V125" t="n">
+        <v>143179</v>
+      </c>
+      <c r="W125" t="n">
+        <v>3041</v>
+      </c>
+      <c r="X125" t="n">
+        <v>1059</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>2031</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>356</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>225</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:44</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>BV1c3gF6wERf</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>【杨博文】元气甜度爆表！摇曳4k横屏直拍</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>游园会_杨博文</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
+        <v>392983</v>
+      </c>
+      <c r="W126" t="n">
+        <v>8294</v>
+      </c>
+      <c r="X126" t="n">
+        <v>3235</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>5618</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>892</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>1770</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:48</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>BV18ZgH6uEYv</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="V127" t="n">
+        <v>37918</v>
+      </c>
+      <c r="W127" t="n">
+        <v>12211</v>
+      </c>
+      <c r="X127" t="n">
+        <v>11212</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>7616</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>483</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:45:52</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>红色防吞3</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>我要在森林里盖房子</t>
+        </is>
+      </c>
+      <c r="V128" t="n">
+        <v>12936</v>
+      </c>
+      <c r="W128" t="n">
+        <v>5</v>
+      </c>
+      <c r="X128" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1421,23 +1421,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>关键时刻来瓶尖叫</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.1157</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1449,42 +1453,42 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>45.67%</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1774.9:1</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1702,12 +1706,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 14:49:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1752,12 +1756,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1802,12 +1806,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1852,12 +1856,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1902,12 +1906,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1952,12 +1956,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2002,12 +2006,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2052,12 +2056,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2102,12 +2106,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2152,12 +2156,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2202,12 +2206,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2246,6 +2250,610 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J23" t="n">
+        <v>380</v>
+      </c>
+      <c r="K23" t="n">
+        <v>102</v>
+      </c>
+      <c r="L23" t="n">
+        <v>276</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2260,7 +2868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2388,12 +2996,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 14:49:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2438,12 +3046,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2488,12 +3096,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2538,12 +3146,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2588,12 +3196,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2638,12 +3246,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2688,12 +3296,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2738,12 +3346,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2788,12 +3396,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2838,12 +3446,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2888,12 +3496,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2932,6 +3540,610 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BV1k9gw6gE4U</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BV1mX8z6NEzz</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J23" t="n">
+        <v>380</v>
+      </c>
+      <c r="K23" t="n">
+        <v>102</v>
+      </c>
+      <c r="L23" t="n">
+        <v>276</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1421,27 +1421,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1157</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1453,42 +1449,42 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1774.9:1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,12 +1752,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 15:19:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1806,7 +1802,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1856,12 +1852,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1906,12 +1902,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1956,12 +1952,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2006,12 +2002,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2056,12 +2052,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2106,12 +2102,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2156,12 +2152,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2206,12 +2202,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2256,12 +2252,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2306,12 +2302,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2356,12 +2352,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2406,12 +2402,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2456,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2506,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2556,12 +2552,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2606,12 +2602,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2656,12 +2652,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2706,66 +2702,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2810,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2854,6 +2846,610 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:35</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J33" t="n">
+        <v>380</v>
+      </c>
+      <c r="K33" t="n">
+        <v>102</v>
+      </c>
+      <c r="L33" t="n">
+        <v>276</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2868,7 +3464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,12 +3642,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 15:19:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3096,7 +3692,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3146,12 +3742,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3196,12 +3792,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3246,12 +3842,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3296,12 +3892,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3346,12 +3942,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3396,12 +3992,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3446,12 +4042,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3496,12 +4092,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3546,12 +4142,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3596,12 +4192,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3646,12 +4242,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3696,12 +4292,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3746,12 +4342,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3796,12 +4392,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3846,12 +4442,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3896,12 +4492,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3946,12 +4542,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3996,66 +4592,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4100,12 +4692,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4144,6 +4736,610 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BV1qHbb6QErY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:35</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J33" t="n">
+        <v>380</v>
+      </c>
+      <c r="K33" t="n">
+        <v>102</v>
+      </c>
+      <c r="L33" t="n">
+        <v>276</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,12 +1802,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 15:45:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1902,7 +1902,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1952,12 +1952,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2002,12 +2002,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2052,7 +2052,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2202,12 +2202,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,12 +2352,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2402,12 +2402,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2502,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2552,12 +2552,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,66 +3202,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3300,18 +3296,18 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3356,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3406,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3450,6 +3446,610 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:35</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:32</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J43" t="n">
+        <v>380</v>
+      </c>
+      <c r="K43" t="n">
+        <v>102</v>
+      </c>
+      <c r="L43" t="n">
+        <v>276</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3464,7 +4064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3692,12 +4292,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 15:45:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3742,7 +4342,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3792,7 +4392,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3842,12 +4442,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3892,12 +4492,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3942,7 +4542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3992,12 +4592,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4042,12 +4642,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4092,12 +4692,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4142,12 +4742,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4192,12 +4792,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4242,12 +4842,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4292,12 +4892,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4342,12 +4942,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4392,12 +4992,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4442,12 +5042,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4492,12 +5092,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4542,12 +5142,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4592,12 +5192,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4642,12 +5242,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4692,12 +5292,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4742,12 +5342,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4792,12 +5392,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4842,12 +5442,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4892,12 +5492,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4942,12 +5542,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4992,12 +5592,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5042,12 +5642,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5092,66 +5692,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5190,18 +5786,18 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5246,12 +5842,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5296,12 +5892,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5340,6 +5936,610 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:32</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:35</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:32</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J43" t="n">
+        <v>380</v>
+      </c>
+      <c r="K43" t="n">
+        <v>102</v>
+      </c>
+      <c r="L43" t="n">
+        <v>276</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,12 +1852,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 16:20:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1902,7 +1902,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,12 +2352,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2502,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2552,12 +2552,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,12 +3602,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,66 +3702,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3800,18 +3796,18 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3856,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3906,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3956,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4006,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4050,6 +4046,610 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:32</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J53" t="n">
+        <v>380</v>
+      </c>
+      <c r="K53" t="n">
+        <v>102</v>
+      </c>
+      <c r="L53" t="n">
+        <v>276</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4064,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4342,12 +4942,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 16:20:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4392,7 +4992,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4442,7 +5042,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4492,7 +5092,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4542,12 +5142,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4592,12 +5192,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4642,7 +5242,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4692,7 +5292,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4742,12 +5342,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4792,12 +5392,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4842,12 +5442,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4892,7 +5492,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4942,12 +5542,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4992,12 +5592,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5042,12 +5642,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5092,12 +5692,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5142,12 +5742,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5192,12 +5792,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5242,12 +5842,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5292,12 +5892,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5342,12 +5942,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5392,12 +5992,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5442,12 +6042,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5492,12 +6092,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5542,12 +6142,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5592,12 +6192,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5642,12 +6242,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5692,12 +6292,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5742,12 +6342,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5792,12 +6392,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5842,12 +6442,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5892,12 +6492,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5942,12 +6542,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5992,12 +6592,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6042,12 +6642,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6092,12 +6692,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6142,12 +6742,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6192,66 +6792,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6290,18 +6886,18 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6346,12 +6942,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6396,12 +6992,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6446,12 +7042,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6496,12 +7092,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6540,6 +7136,610 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:32</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BV1r8eV6fE5N</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J53" t="n">
+        <v>380</v>
+      </c>
+      <c r="K53" t="n">
+        <v>102</v>
+      </c>
+      <c r="L53" t="n">
+        <v>276</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,12 +1902,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 16:45:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2052,7 +2052,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2202,12 +2202,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,12 +2402,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2502,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,12 +3602,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,66 +4202,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4300,18 +4296,18 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4356,12 +4352,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4406,12 +4402,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4456,12 +4452,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4506,12 +4502,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4556,12 +4552,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4606,12 +4602,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4650,6 +4646,610 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J63" t="n">
+        <v>380</v>
+      </c>
+      <c r="K63" t="n">
+        <v>102</v>
+      </c>
+      <c r="L63" t="n">
+        <v>276</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4664,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4992,12 +5592,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 16:45:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5042,7 +5642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5092,7 +5692,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5142,7 +5742,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5192,7 +5792,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5242,12 +5842,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5292,12 +5892,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5342,7 +5942,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5392,7 +5992,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5442,7 +6042,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5492,12 +6092,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5542,12 +6142,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5592,12 +6192,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5642,7 +6242,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5692,7 +6292,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5742,12 +6342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5792,12 +6392,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5842,12 +6442,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5892,12 +6492,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5942,7 +6542,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5992,12 +6592,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6042,12 +6642,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6092,12 +6692,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6142,12 +6742,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6192,12 +6792,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6242,12 +6842,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6292,12 +6892,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6342,12 +6942,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6392,12 +6992,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6442,12 +7042,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6492,12 +7092,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6542,12 +7142,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6592,12 +7192,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6642,12 +7242,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6692,12 +7292,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6742,12 +7342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6792,12 +7392,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6842,12 +7442,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6892,12 +7492,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6942,12 +7542,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6992,12 +7592,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7042,12 +7642,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7092,12 +7692,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7142,12 +7742,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7192,12 +7792,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7242,12 +7842,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7292,66 +7892,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7390,18 +7986,18 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7446,12 +8042,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7496,12 +8092,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7546,12 +8142,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7596,12 +8192,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7646,12 +8242,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7696,12 +8292,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7740,6 +8336,610 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J63" t="n">
+        <v>380</v>
+      </c>
+      <c r="K63" t="n">
+        <v>102</v>
+      </c>
+      <c r="L63" t="n">
+        <v>276</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1121,23 +1121,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Astra_杨博文</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0964</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1149,42 +1153,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34.81%</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>637.1:1</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,12 +1956,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 17:19:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2002,7 +2006,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2052,7 +2056,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2102,7 +2106,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2152,7 +2156,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2202,7 +2206,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2252,12 +2256,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2302,12 +2306,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,7 +2356,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2406,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2456,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2506,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,12 +2556,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2602,12 +2606,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2652,12 +2656,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2702,7 +2706,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2756,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2806,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,12 +2856,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2902,12 +2906,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,12 +2956,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,12 +3006,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,7 +3056,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3106,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,12 +3156,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,12 +3206,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3252,12 +3256,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,12 +3306,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,12 +3356,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,7 +3406,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,12 +3456,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,12 +3506,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3552,12 +3556,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,12 +3606,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,12 +3656,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,12 +3706,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3752,12 +3756,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3802,12 +3806,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3852,12 +3856,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3902,12 +3906,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3952,12 +3956,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,12 +4006,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4052,62 +4056,66 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,12 +4160,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,12 +4210,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4252,12 +4260,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4302,12 +4310,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4352,12 +4360,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4402,12 +4410,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,12 +4460,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4502,12 +4510,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4552,12 +4560,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4602,12 +4610,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4652,12 +4660,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4702,66 +4710,62 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4800,18 +4804,18 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4856,12 +4860,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4906,12 +4910,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4956,12 +4960,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5006,12 +5010,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5056,12 +5060,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5106,12 +5110,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5156,12 +5160,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5206,50 +5210,654 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J73" t="n">
+        <v>380</v>
+      </c>
+      <c r="K73" t="n">
+        <v>102</v>
+      </c>
+      <c r="L73" t="n">
+        <v>276</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>2026-09-18 16:45:48</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>BV1xebR6zEkr</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5264,7 +5872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5642,12 +6250,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 17:19:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5692,7 +6300,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5742,7 +6350,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5792,7 +6400,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5842,7 +6450,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5892,7 +6500,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5942,12 +6550,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5992,12 +6600,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6042,7 +6650,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6092,7 +6700,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6142,7 +6750,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6192,7 +6800,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6242,12 +6850,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6292,12 +6900,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6342,12 +6950,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6392,7 +7000,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6442,7 +7050,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6492,7 +7100,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6542,12 +7150,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6592,12 +7200,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6642,12 +7250,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6692,12 +7300,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6742,7 +7350,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6792,7 +7400,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6842,12 +7450,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6892,12 +7500,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6942,12 +7550,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6992,12 +7600,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7042,12 +7650,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7092,7 +7700,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7142,12 +7750,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7192,12 +7800,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7242,12 +7850,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7292,12 +7900,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7342,12 +7950,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7392,12 +8000,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7442,12 +8050,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7492,12 +8100,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7542,12 +8150,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7592,12 +8200,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7642,12 +8250,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7692,12 +8300,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7742,62 +8350,66 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7842,12 +8454,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7892,12 +8504,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7942,12 +8554,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7992,12 +8604,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8042,12 +8654,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8092,12 +8704,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8142,12 +8754,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8192,12 +8804,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8242,12 +8854,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8292,12 +8904,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8342,12 +8954,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8392,66 +9004,62 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8490,18 +9098,18 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8546,12 +9154,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8596,12 +9204,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8646,12 +9254,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8696,12 +9304,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8746,12 +9354,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8796,12 +9404,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8846,12 +9454,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8896,50 +9504,654 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>2026-09-18 14:49:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>181043</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4449</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3318</v>
+      </c>
+      <c r="J73" t="n">
+        <v>380</v>
+      </c>
+      <c r="K73" t="n">
+        <v>102</v>
+      </c>
+      <c r="L73" t="n">
+        <v>276</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>181043</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:29</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-181043</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>2026-09-18 16:45:48</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>BV1xebR6zEkr</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1121,27 +1121,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0964</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,42 +1149,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>34.81%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>637.1:1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2006,12 +2002,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 17:44:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2056,7 +2052,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2106,7 +2102,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2156,7 +2152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2206,7 +2202,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2256,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2306,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2356,12 +2352,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2406,12 +2402,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2456,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2556,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2606,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2656,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2706,12 +2702,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2756,12 +2752,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2806,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2856,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2906,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2956,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3056,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3106,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3156,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3206,12 +3202,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3256,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3306,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3356,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3406,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3456,12 +3452,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3506,12 +3502,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3556,12 +3552,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3606,12 +3602,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3656,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3706,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3756,12 +3752,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3806,12 +3802,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3856,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3906,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3956,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4006,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4056,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4066,56 +4062,52 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4160,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4210,12 +4202,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4260,12 +4252,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4310,12 +4302,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4360,62 +4352,66 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4454,18 +4450,18 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4510,12 +4506,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4560,12 +4556,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4610,12 +4606,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4660,12 +4656,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4710,12 +4706,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4760,12 +4756,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4810,12 +4806,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4860,12 +4856,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4910,12 +4906,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4960,12 +4956,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5010,12 +5006,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5060,12 +5056,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5110,12 +5106,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5160,12 +5156,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5210,66 +5206,62 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5308,18 +5300,18 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5364,12 +5356,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5414,12 +5406,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5464,12 +5456,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5514,12 +5506,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5564,12 +5556,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5614,12 +5606,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5664,12 +5656,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5714,62 +5706,66 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5808,18 +5804,18 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5858,6 +5854,606 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:58</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5872,7 +6468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6300,12 +6896,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 17:44:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6350,7 +6946,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6400,7 +6996,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6450,7 +7046,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6500,7 +7096,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6550,7 +7146,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6600,7 +7196,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6650,12 +7246,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6700,12 +7296,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6750,7 +7346,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6800,7 +7396,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6850,7 +7446,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6900,7 +7496,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6950,7 +7546,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7000,12 +7596,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7050,12 +7646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7100,12 +7696,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7150,7 +7746,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7200,7 +7796,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7250,7 +7846,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7300,7 +7896,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7350,12 +7946,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7400,12 +7996,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7450,12 +8046,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7500,12 +8096,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7550,7 +8146,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7600,7 +8196,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7650,7 +8246,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7700,12 +8296,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7750,12 +8346,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7800,12 +8396,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7850,12 +8446,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7900,12 +8496,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7950,7 +8546,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8000,7 +8596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8050,12 +8646,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8100,12 +8696,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8150,12 +8746,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8200,12 +8796,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8250,12 +8846,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8300,12 +8896,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8350,7 +8946,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8360,56 +8956,52 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8454,12 +9046,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8504,12 +9096,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8554,12 +9146,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8604,12 +9196,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8654,62 +9246,66 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8748,18 +9344,18 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8804,12 +9400,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8854,12 +9450,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8904,12 +9500,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8954,12 +9550,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9004,12 +9600,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9054,12 +9650,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9104,12 +9700,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9154,12 +9750,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9204,12 +9800,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9254,12 +9850,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9304,12 +9900,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9354,12 +9950,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9404,12 +10000,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9454,12 +10050,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9504,66 +10100,62 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9602,18 +10194,18 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9658,12 +10250,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9708,12 +10300,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9758,12 +10350,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9808,12 +10400,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9858,12 +10450,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9908,12 +10500,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9958,12 +10550,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10008,62 +10600,66 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10102,18 +10698,18 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -10152,6 +10748,606 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:55</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:58</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,12 +2052,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 18:19:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2502,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4252,12 +4252,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4362,51 +4362,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4450,18 +4446,18 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4506,12 +4502,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4556,12 +4552,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4606,12 +4602,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4656,62 +4652,66 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4750,18 +4750,18 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4856,12 +4856,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4906,12 +4906,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4956,12 +4956,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5006,12 +5006,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5056,12 +5056,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5106,12 +5106,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5156,12 +5156,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5206,12 +5206,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5256,12 +5256,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5306,12 +5306,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5356,12 +5356,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5406,12 +5406,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5506,12 +5506,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5556,12 +5556,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5606,12 +5606,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5656,12 +5656,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5706,66 +5706,62 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5804,18 +5800,18 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5860,12 +5856,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5910,12 +5906,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5960,12 +5956,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6010,12 +6006,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6060,12 +6056,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6110,12 +6106,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6160,12 +6156,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6210,62 +6206,66 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6304,18 +6304,18 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6360,12 +6360,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6410,12 +6410,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6454,6 +6454,606 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:58</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6468,7 +7068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6946,12 +7546,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 18:19:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6996,7 +7596,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7046,7 +7646,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7096,7 +7696,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7146,7 +7746,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7196,7 +7796,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7246,7 +7846,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7296,7 +7896,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7346,12 +7946,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7396,12 +7996,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7446,7 +8046,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7496,7 +8096,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7546,7 +8146,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7596,7 +8196,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7646,7 +8246,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7696,7 +8296,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7746,12 +8346,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7796,12 +8396,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7846,12 +8446,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7896,7 +8496,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7946,7 +8546,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7996,7 +8596,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8046,7 +8646,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8096,7 +8696,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8146,12 +8746,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8196,12 +8796,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8246,12 +8846,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8296,12 +8896,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8346,7 +8946,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8396,7 +8996,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8446,7 +9046,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8496,7 +9096,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8546,12 +9146,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8596,12 +9196,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8646,12 +9246,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8696,12 +9296,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8746,12 +9346,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8796,7 +9396,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8846,7 +9446,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8896,7 +9496,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8946,12 +9546,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8996,12 +9596,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9046,12 +9646,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9096,12 +9696,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9146,12 +9746,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9196,12 +9796,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9246,7 +9846,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9256,51 +9856,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9344,18 +9940,18 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9400,12 +9996,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9450,12 +10046,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9500,12 +10096,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9550,62 +10146,66 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9644,18 +10244,18 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9700,7 +10300,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9750,12 +10350,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9800,12 +10400,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9850,12 +10450,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9900,12 +10500,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9950,12 +10550,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10000,12 +10600,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10050,12 +10650,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10100,12 +10700,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10150,12 +10750,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10200,12 +10800,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10250,12 +10850,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10300,12 +10900,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10350,12 +10950,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10400,12 +11000,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10450,12 +11050,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -10500,12 +11100,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -10550,12 +11150,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10600,66 +11200,62 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10698,18 +11294,18 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -10754,12 +11350,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -10804,12 +11400,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10854,12 +11450,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10904,12 +11500,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10954,12 +11550,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11004,12 +11600,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11054,12 +11650,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11104,62 +11700,66 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -11198,18 +11798,18 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11254,12 +11854,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11304,12 +11904,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11348,6 +11948,606 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:19:07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:58</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,12 +2102,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 18:45:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,12 +2552,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,12 +3602,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,12 +4352,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,12 +4452,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4662,51 +4662,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4750,13 +4746,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4806,12 +4802,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4856,12 +4852,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4906,12 +4902,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4956,62 +4952,66 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5050,18 +5050,18 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5106,12 +5106,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5256,12 +5256,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5306,12 +5306,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5356,12 +5356,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5406,12 +5406,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5506,12 +5506,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5556,12 +5556,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5606,12 +5606,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5756,12 +5756,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5806,12 +5806,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5856,12 +5856,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5906,12 +5906,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5956,12 +5956,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6006,12 +6006,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6106,12 +6106,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6206,66 +6206,62 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6304,18 +6300,18 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6360,12 +6356,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6410,12 +6406,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6460,12 +6456,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6510,12 +6506,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6560,12 +6556,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6610,12 +6606,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6660,12 +6656,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6710,62 +6706,66 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6804,18 +6804,18 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6860,12 +6860,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6960,12 +6960,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7010,12 +7010,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7054,6 +7054,606 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7068,7 +7668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7596,12 +8196,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 18:45:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7646,7 +8246,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7696,7 +8296,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7746,7 +8346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7796,7 +8396,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7846,7 +8446,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7896,7 +8496,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7946,7 +8546,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7996,7 +8596,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8046,12 +8646,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8096,12 +8696,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8146,7 +8746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8196,7 +8796,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8246,7 +8846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8296,7 +8896,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8346,7 +8946,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8396,7 +8996,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8446,7 +9046,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8496,12 +9096,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8546,12 +9146,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8596,12 +9196,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8646,7 +9246,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8696,7 +9296,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8746,7 +9346,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8796,7 +9396,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8846,7 +9446,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8896,7 +9496,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8946,12 +9546,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8996,12 +9596,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9046,12 +9646,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9096,12 +9696,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9146,7 +9746,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9196,7 +9796,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9246,7 +9846,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9296,7 +9896,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9346,7 +9946,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9396,12 +9996,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9446,12 +10046,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9496,12 +10096,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9546,12 +10146,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9596,12 +10196,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9646,7 +10246,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9696,7 +10296,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9746,7 +10346,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9796,7 +10396,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9846,12 +10446,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9896,12 +10496,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9946,12 +10546,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9996,12 +10596,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10046,12 +10646,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10096,12 +10696,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10146,7 +10746,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10156,51 +10756,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10244,13 +10840,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10300,12 +10896,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10350,12 +10946,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10400,12 +10996,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10450,62 +11046,66 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10544,18 +11144,18 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10600,12 +11200,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10650,7 +11250,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10700,7 +11300,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10750,12 +11350,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10800,12 +11400,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10850,12 +11450,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10900,12 +11500,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10950,12 +11550,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11000,12 +11600,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11050,12 +11650,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11100,12 +11700,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11150,7 +11750,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11200,12 +11800,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11250,12 +11850,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11300,12 +11900,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11350,12 +11950,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11400,12 +12000,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11450,12 +12050,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -11500,12 +12100,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11550,12 +12150,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11600,12 +12200,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11650,12 +12250,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11700,66 +12300,62 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -11798,18 +12394,18 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11854,12 +12450,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11904,12 +12500,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11954,12 +12550,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12004,12 +12600,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12054,12 +12650,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12104,12 +12700,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -12154,12 +12750,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12204,62 +12800,66 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12298,18 +12898,18 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12354,12 +12954,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12404,12 +13004,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12454,12 +13054,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12504,12 +13104,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12548,6 +13148,606 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2152,12 +2152,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 19:18:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4252,12 +4252,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4352,12 +4352,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4702,12 +4702,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4752,12 +4752,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4802,12 +4802,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4852,12 +4852,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4962,51 +4962,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5050,13 +5046,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5106,7 +5102,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5156,12 +5152,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5206,12 +5202,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5256,62 +5252,66 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5350,18 +5350,18 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5406,12 +5406,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5506,7 +5506,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5556,7 +5556,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5656,12 +5656,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5756,12 +5756,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5806,12 +5806,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5856,12 +5856,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5906,12 +5906,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5956,12 +5956,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6006,12 +6006,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6056,7 +6056,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6106,7 +6106,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6206,12 +6206,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6256,12 +6256,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6306,12 +6306,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6356,12 +6356,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6406,12 +6406,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6456,12 +6456,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6506,12 +6506,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6556,12 +6556,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6606,7 +6606,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6656,12 +6656,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6706,66 +6706,62 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6804,18 +6800,18 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6860,12 +6856,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6910,12 +6906,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6960,12 +6956,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7010,12 +7006,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7060,12 +7056,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7110,12 +7106,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7160,12 +7156,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7210,62 +7206,66 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7304,18 +7304,18 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7360,12 +7360,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7410,12 +7410,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7510,12 +7510,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7560,12 +7560,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7610,12 +7610,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7654,6 +7654,606 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7668,7 +8268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8246,12 +8846,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 19:18:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8296,7 +8896,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8346,7 +8946,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8396,7 +8996,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8446,7 +9046,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8496,7 +9096,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8546,7 +9146,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8596,7 +9196,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8646,7 +9246,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8696,7 +9296,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8746,12 +9346,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8796,12 +9396,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8846,7 +9446,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8896,7 +9496,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8946,7 +9546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8996,7 +9596,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9046,7 +9646,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9096,7 +9696,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9146,7 +9746,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9196,7 +9796,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9246,12 +9846,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9296,12 +9896,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9346,12 +9946,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9396,7 +9996,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9446,7 +10046,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9496,7 +10096,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9546,7 +10146,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9596,7 +10196,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9646,7 +10246,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9696,7 +10296,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9746,12 +10346,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9796,12 +10396,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9846,12 +10446,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9896,12 +10496,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9946,7 +10546,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9996,7 +10596,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10046,7 +10646,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10096,7 +10696,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10146,7 +10746,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10196,7 +10796,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10246,12 +10846,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10296,12 +10896,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -10346,12 +10946,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -10396,12 +10996,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10446,12 +11046,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10496,7 +11096,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10546,7 +11146,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10596,7 +11196,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10646,7 +11246,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10696,7 +11296,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10746,12 +11346,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10796,12 +11396,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10846,12 +11446,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10896,12 +11496,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10946,12 +11546,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10996,12 +11596,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11046,7 +11646,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11056,51 +11656,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -11144,13 +11740,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -11200,7 +11796,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -11250,12 +11846,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11300,12 +11896,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11350,62 +11946,66 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11444,18 +12044,18 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11500,12 +12100,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11550,12 +12150,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11600,7 +12200,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11650,7 +12250,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11700,7 +12300,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11750,12 +12350,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11800,12 +12400,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11850,12 +12450,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11900,12 +12500,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11950,12 +12550,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -12000,12 +12600,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12050,12 +12650,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12100,12 +12700,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12150,7 +12750,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -12200,7 +12800,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -12250,12 +12850,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12300,12 +12900,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12350,12 +12950,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12400,12 +13000,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -12450,12 +13050,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -12500,12 +13100,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -12550,12 +13150,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12600,12 +13200,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12650,12 +13250,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12700,7 +13300,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -12750,12 +13350,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12800,66 +13400,62 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12898,18 +13494,18 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12954,12 +13550,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13004,12 +13600,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13054,12 +13650,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13104,12 +13700,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13154,12 +13750,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -13204,12 +13800,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -13254,12 +13850,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13304,62 +13900,66 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13398,18 +13998,18 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13454,12 +14054,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13504,12 +14104,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -13554,12 +14154,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13604,12 +14204,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13654,12 +14254,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13704,12 +14304,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13748,6 +14348,606 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BV1rqgW6hEvv</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2202,12 +2202,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 19:44:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,12 +4452,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,12 +4952,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5002,12 +5002,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5052,12 +5052,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5102,12 +5102,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5202,12 +5202,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5262,51 +5262,47 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5350,13 +5346,13 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5406,7 +5402,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5456,7 +5452,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5506,12 +5502,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5556,62 +5552,66 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5650,18 +5650,18 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5756,12 +5756,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5806,12 +5806,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5956,7 +5956,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6106,12 +6106,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6206,12 +6206,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6256,12 +6256,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6306,12 +6306,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6356,12 +6356,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6406,12 +6406,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6506,7 +6506,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6556,7 +6556,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6656,12 +6656,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6706,12 +6706,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6756,12 +6756,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6806,12 +6806,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6856,12 +6856,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6906,12 +6906,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6956,12 +6956,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7006,12 +7006,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7056,7 +7056,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7106,7 +7106,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7156,12 +7156,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7206,66 +7206,62 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7304,18 +7300,18 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7360,12 +7356,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7410,12 +7406,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7460,12 +7456,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7510,12 +7506,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7560,12 +7556,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7610,12 +7606,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7660,7 +7656,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7710,62 +7706,66 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7804,18 +7804,18 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7860,12 +7860,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7910,12 +7910,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7960,12 +7960,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8010,12 +8010,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8060,12 +8060,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8110,12 +8110,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8160,12 +8160,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8210,12 +8210,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8254,6 +8254,606 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8268,7 +8868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8896,12 +9496,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 19:44:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8946,7 +9546,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8996,7 +9596,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9046,7 +9646,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9096,7 +9696,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9146,7 +9746,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9196,7 +9796,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9246,7 +9846,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9296,7 +9896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9346,7 +9946,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9396,7 +9996,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9446,12 +10046,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9496,12 +10096,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9546,7 +10146,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9596,7 +10196,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9646,7 +10246,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9696,7 +10296,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9746,7 +10346,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9796,7 +10396,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9846,7 +10446,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9896,7 +10496,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9946,7 +10546,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9996,12 +10596,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10046,12 +10646,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10096,12 +10696,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10146,7 +10746,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10196,7 +10796,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10246,7 +10846,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10296,7 +10896,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10346,7 +10946,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10396,7 +10996,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10446,7 +11046,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10496,7 +11096,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10546,12 +11146,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10596,12 +11196,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10646,12 +11246,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10696,12 +11296,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10746,7 +11346,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10796,7 +11396,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10846,7 +11446,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10896,7 +11496,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10946,7 +11546,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10996,7 +11596,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11046,7 +11646,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11096,12 +11696,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11146,12 +11746,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11196,12 +11796,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11246,12 +11846,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -11296,12 +11896,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11346,7 +11946,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11396,7 +11996,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11446,7 +12046,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11496,7 +12096,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11546,7 +12146,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11596,7 +12196,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11646,12 +12246,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11696,12 +12296,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11746,12 +12346,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11796,12 +12396,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11846,12 +12446,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11896,12 +12496,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11946,7 +12546,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -11956,51 +12556,47 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12044,13 +12640,13 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12100,7 +12696,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12150,7 +12746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12200,12 +12796,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12250,62 +12846,66 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -12344,18 +12944,18 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12400,12 +13000,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12450,12 +13050,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -12500,12 +13100,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12550,7 +13150,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -12600,7 +13200,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -12650,7 +13250,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -12700,7 +13300,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -12750,12 +13350,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12800,12 +13400,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12850,12 +13450,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12900,12 +13500,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12950,12 +13550,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -13000,12 +13600,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13050,12 +13650,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -13100,12 +13700,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -13150,7 +13750,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -13200,7 +13800,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -13250,7 +13850,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -13300,12 +13900,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13350,12 +13950,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -13400,12 +14000,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -13450,12 +14050,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -13500,12 +14100,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13550,12 +14150,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13600,12 +14200,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13650,12 +14250,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13700,12 +14300,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13750,7 +14350,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -13800,7 +14400,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13850,12 +14450,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13900,66 +14500,62 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13998,18 +14594,18 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14054,12 +14650,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14104,12 +14700,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14154,12 +14750,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14204,12 +14800,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -14254,12 +14850,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -14304,12 +14900,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -14354,7 +14950,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -14404,62 +15000,66 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14498,18 +15098,18 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14554,12 +15154,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14604,12 +15204,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14654,12 +15254,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14704,12 +15304,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14754,12 +15354,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14804,12 +15404,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14854,12 +15454,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14904,12 +15504,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14948,6 +15548,606 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:24:15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,12 +2252,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 20:23:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,12 +2852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4702,12 +4702,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4752,12 +4752,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4802,12 +4802,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4852,12 +4852,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5252,12 +5252,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5352,12 +5352,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5452,12 +5452,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5502,12 +5502,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5562,51 +5562,47 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5650,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5706,7 +5702,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5756,7 +5752,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5806,7 +5802,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5856,62 +5852,66 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5950,18 +5950,18 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6006,12 +6006,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6106,12 +6106,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6306,7 +6306,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6356,7 +6356,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6456,12 +6456,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6506,12 +6506,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6556,12 +6556,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6656,12 +6656,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6706,12 +6706,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6756,12 +6756,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6806,12 +6806,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6856,7 +6856,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6906,7 +6906,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6956,7 +6956,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7006,7 +7006,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7106,12 +7106,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7156,12 +7156,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7206,12 +7206,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7306,12 +7306,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7356,12 +7356,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7506,7 +7506,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7706,66 +7706,62 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7804,18 +7800,18 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7860,12 +7856,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7910,12 +7906,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7960,12 +7956,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8010,12 +8006,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8060,12 +8056,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8110,12 +8106,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8160,7 +8156,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8210,7 +8206,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8220,52 +8216,56 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8304,18 +8304,18 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8360,12 +8360,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8410,12 +8410,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8460,12 +8460,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8510,12 +8510,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8560,12 +8560,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8610,12 +8610,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8660,12 +8660,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8710,12 +8710,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8760,12 +8760,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8854,6 +8854,606 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8868,7 +9468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9546,12 +10146,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 20:23:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9596,7 +10196,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9646,7 +10246,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9696,7 +10296,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9746,7 +10346,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9796,7 +10396,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9846,7 +10446,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9896,7 +10496,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9946,7 +10546,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9996,7 +10596,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10046,7 +10646,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10096,7 +10696,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10146,12 +10746,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10196,12 +10796,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10246,7 +10846,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10296,7 +10896,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10346,7 +10946,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10396,7 +10996,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10446,7 +11046,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -10496,7 +11096,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10546,7 +11146,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10596,7 +11196,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10646,7 +11246,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10696,7 +11296,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10746,12 +11346,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10796,12 +11396,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10846,12 +11446,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10896,7 +11496,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10946,7 +11546,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10996,7 +11596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11046,7 +11646,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11096,7 +11696,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11146,7 +11746,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -11196,7 +11796,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11246,7 +11846,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11296,7 +11896,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -11346,12 +11946,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11396,12 +11996,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11446,12 +12046,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11496,12 +12096,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11546,7 +12146,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -11596,7 +12196,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11646,7 +12246,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11696,7 +12296,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11746,7 +12346,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11796,7 +12396,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11846,7 +12446,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11896,7 +12496,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11946,12 +12546,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11996,12 +12596,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12046,12 +12646,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12096,12 +12696,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -12146,12 +12746,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12196,7 +12796,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -12246,7 +12846,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -12296,7 +12896,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12346,7 +12946,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -12396,7 +12996,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -12446,7 +13046,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12496,7 +13096,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12546,12 +13146,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12596,12 +13196,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12646,12 +13246,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12696,12 +13296,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12746,12 +13346,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12796,12 +13396,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12846,7 +13446,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12856,51 +13456,47 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12944,13 +13540,13 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -13000,7 +13596,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -13050,7 +13646,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -13100,7 +13696,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -13150,62 +13746,66 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -13244,18 +13844,18 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -13300,12 +13900,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -13350,12 +13950,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -13400,12 +14000,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -13450,12 +14050,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -13500,7 +14100,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -13550,7 +14150,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -13600,7 +14200,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -13650,7 +14250,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -13700,7 +14300,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -13750,12 +14350,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13800,12 +14400,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13850,12 +14450,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -13900,12 +14500,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13950,12 +14550,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -14000,12 +14600,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14050,12 +14650,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14100,12 +14700,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14150,7 +14750,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -14200,7 +14800,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -14250,7 +14850,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -14300,7 +14900,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -14350,12 +14950,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -14400,12 +15000,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -14450,12 +15050,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -14500,12 +15100,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -14550,12 +15150,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -14600,12 +15200,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14650,12 +15250,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14700,12 +15300,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14750,12 +15350,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14800,7 +15400,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -14850,7 +15450,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -14900,7 +15500,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -14950,12 +15550,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15000,66 +15600,62 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -15098,18 +15694,18 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15154,12 +15750,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -15204,12 +15800,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -15254,12 +15850,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -15304,12 +15900,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -15354,12 +15950,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -15404,12 +16000,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -15454,7 +16050,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -15504,7 +16100,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -15514,52 +16110,56 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15598,18 +16198,18 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15654,12 +16254,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15704,12 +16304,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15754,12 +16354,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15804,12 +16404,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15854,12 +16454,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15904,12 +16504,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15954,12 +16554,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -16004,12 +16604,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -16054,12 +16654,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -16104,7 +16704,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -16148,6 +16748,606 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:49:18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N157"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,12 +2302,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 20:49:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,12 +3602,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,12 +4252,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4352,12 +4352,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4952,12 +4952,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5002,12 +5002,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5052,12 +5052,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5102,12 +5102,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5452,7 +5452,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5552,12 +5552,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5652,12 +5652,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5702,12 +5702,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5752,12 +5752,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5802,12 +5802,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5852,7 +5852,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5862,51 +5862,47 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5950,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6006,7 +6002,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6056,7 +6052,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6106,7 +6102,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6156,7 +6152,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6166,52 +6162,56 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6250,18 +6250,18 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6306,12 +6306,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6356,12 +6356,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6406,12 +6406,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6456,12 +6456,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6506,12 +6506,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6556,7 +6556,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6606,7 +6606,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6856,12 +6856,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6906,12 +6906,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6956,12 +6956,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7006,12 +7006,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7106,12 +7106,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7156,12 +7156,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7206,12 +7206,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7306,7 +7306,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7356,7 +7356,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7406,7 +7406,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7456,7 +7456,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7506,12 +7506,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7556,12 +7556,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7706,12 +7706,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7756,12 +7756,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7856,12 +7856,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7906,12 +7906,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8056,7 +8056,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8156,12 +8156,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8206,66 +8206,62 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8304,18 +8300,18 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8360,12 +8356,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8410,12 +8406,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8460,12 +8456,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8510,12 +8506,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8560,12 +8556,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8610,12 +8606,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8660,7 +8656,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8710,7 +8706,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8720,47 +8716,51 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8804,18 +8804,18 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8860,12 +8860,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8910,12 +8910,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8960,12 +8960,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9010,12 +9010,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9060,12 +9060,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9110,12 +9110,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9160,12 +9160,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9210,12 +9210,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9260,12 +9260,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9310,12 +9310,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9360,7 +9360,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9410,7 +9410,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9454,6 +9454,606 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9468,7 +10068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N157"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10196,12 +10796,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 20:49:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10246,7 +10846,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10296,7 +10896,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10346,7 +10946,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10396,7 +10996,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10446,7 +11046,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10496,7 +11096,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10546,7 +11146,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10596,7 +11196,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10646,7 +11246,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10696,7 +11296,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10746,7 +11346,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10796,7 +11396,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10846,12 +11446,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10896,12 +11496,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10946,7 +11546,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10996,7 +11596,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11046,7 +11646,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11096,7 +11696,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11146,7 +11746,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11196,7 +11796,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11246,7 +11846,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11296,7 +11896,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11346,7 +11946,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11396,7 +11996,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11446,7 +12046,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11496,12 +12096,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11546,12 +12146,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11596,12 +12196,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11646,7 +12246,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11696,7 +12296,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11746,7 +12346,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -11796,7 +12396,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11846,7 +12446,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11896,7 +12496,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -11946,7 +12546,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -11996,7 +12596,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12046,7 +12646,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12096,7 +12696,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12146,12 +12746,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12196,12 +12796,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12246,12 +12846,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -12296,12 +12896,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12346,7 +12946,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12396,7 +12996,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12446,7 +13046,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12496,7 +13096,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12546,7 +13146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12596,7 +13196,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12646,7 +13246,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12696,7 +13296,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12746,7 +13346,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -12796,12 +13396,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12846,12 +13446,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12896,12 +13496,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12946,12 +13546,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12996,12 +13596,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13046,7 +13646,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13096,7 +13696,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13146,7 +13746,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -13196,7 +13796,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -13246,7 +13846,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -13296,7 +13896,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -13346,7 +13946,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13396,7 +13996,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -13446,12 +14046,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13496,12 +14096,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13546,12 +14146,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -13596,12 +14196,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13646,12 +14246,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -13696,12 +14296,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -13746,7 +14346,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -13756,51 +14356,47 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -13844,13 +14440,13 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -13900,7 +14496,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -13950,7 +14546,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -14000,7 +14596,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -14050,7 +14646,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14060,52 +14656,56 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -14144,18 +14744,18 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -14200,12 +14800,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -14250,12 +14850,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -14300,12 +14900,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -14350,12 +14950,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -14400,12 +15000,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -14450,7 +15050,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -14500,7 +15100,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -14550,7 +15150,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -14600,7 +15200,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -14650,7 +15250,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -14700,7 +15300,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -14750,12 +15350,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -14800,12 +15400,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -14850,12 +15450,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14900,12 +15500,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -14950,12 +15550,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -15000,12 +15600,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -15050,12 +15650,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -15100,12 +15700,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -15150,7 +15750,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15200,7 +15800,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15250,7 +15850,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15300,7 +15900,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15350,7 +15950,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -15400,12 +16000,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -15450,12 +16050,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15500,12 +16100,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -15550,12 +16150,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15600,12 +16200,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -15650,12 +16250,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -15700,12 +16300,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15750,12 +16350,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -15800,12 +16400,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -15850,7 +16450,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -15900,7 +16500,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -15950,7 +16550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16000,7 +16600,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -16050,12 +16650,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -16100,66 +16700,62 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -16198,18 +16794,18 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -16254,12 +16850,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -16304,12 +16900,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -16354,12 +16950,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -16404,12 +17000,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -16454,12 +17050,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -16504,12 +17100,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -16554,7 +17150,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -16604,7 +17200,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -16614,47 +17210,51 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -16698,18 +17298,18 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -16754,12 +17354,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -16804,12 +17404,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -16854,12 +17454,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -16904,12 +17504,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16954,12 +17554,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -17004,12 +17604,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -17054,12 +17654,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -17104,12 +17704,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -17154,12 +17754,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -17204,12 +17804,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -17254,7 +17854,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -17304,7 +17904,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -17348,6 +17948,606 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:19:21</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,12 +2352,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 21:18:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,12 +4452,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5202,12 +5202,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5252,12 +5252,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5352,12 +5352,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5452,7 +5452,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5752,7 +5752,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5852,12 +5852,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5902,12 +5902,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5952,12 +5952,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6002,12 +6002,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6052,12 +6052,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6102,12 +6102,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6152,7 +6152,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6162,51 +6162,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6250,13 +6246,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6306,7 +6302,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6356,7 +6352,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6406,7 +6402,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6456,7 +6452,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6466,47 +6462,51 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6550,18 +6550,18 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6656,12 +6656,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6706,12 +6706,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6756,12 +6756,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6806,12 +6806,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6856,12 +6856,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6906,7 +6906,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6956,7 +6956,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7006,7 +7006,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7106,7 +7106,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7156,7 +7156,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7306,12 +7306,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7356,12 +7356,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7506,12 +7506,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7556,12 +7556,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7656,7 +7656,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7706,7 +7706,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7806,7 +7806,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7856,7 +7856,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7906,7 +7906,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7956,12 +7956,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8006,12 +8006,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8056,12 +8056,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8106,12 +8106,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8156,12 +8156,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8206,12 +8206,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8256,12 +8256,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8356,12 +8356,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8506,7 +8506,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8556,7 +8556,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8656,12 +8656,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8706,66 +8706,62 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8804,18 +8800,18 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8860,12 +8856,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8910,12 +8906,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8960,12 +8956,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9010,12 +9006,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9060,12 +9056,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9110,12 +9106,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9160,7 +9156,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9210,7 +9206,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9220,47 +9216,51 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9304,13 +9304,13 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9360,12 +9360,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9410,12 +9410,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9460,12 +9460,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9510,12 +9510,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9560,12 +9560,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9610,12 +9610,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9660,12 +9660,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9710,12 +9710,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9760,12 +9760,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9810,12 +9810,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9860,12 +9860,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9910,7 +9910,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9960,7 +9960,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10010,7 +10010,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10054,6 +10054,606 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10068,7 +10668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10846,12 +11446,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 21:18:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10896,7 +11496,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10946,7 +11546,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10996,7 +11596,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11046,7 +11646,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11096,7 +11696,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11146,7 +11746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11196,7 +11796,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11246,7 +11846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11296,7 +11896,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11346,7 +11946,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11396,7 +11996,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11446,7 +12046,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11496,7 +12096,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11546,12 +12146,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11596,12 +12196,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11646,7 +12246,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11696,7 +12296,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11746,7 +12346,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11796,7 +12396,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11846,7 +12446,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11896,7 +12496,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11946,7 +12546,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11996,7 +12596,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12046,7 +12646,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12096,7 +12696,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12146,7 +12746,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12196,7 +12796,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12246,12 +12846,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12296,12 +12896,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12346,12 +12946,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12396,7 +12996,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12446,7 +13046,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12496,7 +13096,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12546,7 +13146,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12596,7 +13196,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12646,7 +13246,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12696,7 +13296,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12746,7 +13346,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12796,7 +13396,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12846,7 +13446,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12896,7 +13496,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12946,12 +13546,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12996,12 +13596,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -13046,12 +13646,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -13096,12 +13696,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -13146,7 +13746,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13196,7 +13796,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13246,7 +13846,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13296,7 +13896,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13346,7 +13946,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13396,7 +13996,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13446,7 +14046,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13496,7 +14096,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13546,7 +14146,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13596,7 +14196,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13646,12 +14246,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13696,12 +14296,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13746,12 +14346,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13796,12 +14396,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13846,12 +14446,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13896,7 +14496,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -13946,7 +14546,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13996,7 +14596,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -14046,7 +14646,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14096,7 +14696,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14146,7 +14746,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14196,7 +14796,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14246,7 +14846,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14296,7 +14896,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14346,12 +14946,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -14396,12 +14996,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -14446,12 +15046,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14496,12 +15096,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14546,12 +15146,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -14596,12 +15196,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -14646,7 +15246,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14656,51 +15256,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -14744,13 +15340,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14800,7 +15396,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14850,7 +15446,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14900,7 +15496,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -14950,7 +15546,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -14960,47 +15556,51 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15044,18 +15644,18 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -15100,12 +15700,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -15150,12 +15750,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -15200,12 +15800,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -15250,12 +15850,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -15300,12 +15900,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -15350,12 +15950,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -15400,7 +16000,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -15450,7 +16050,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15500,7 +16100,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -15550,7 +16150,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -15600,7 +16200,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -15650,7 +16250,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -15700,7 +16300,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15750,12 +16350,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -15800,12 +16400,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -15850,12 +16450,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -15900,12 +16500,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15950,12 +16550,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -16000,12 +16600,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -16050,12 +16650,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -16100,12 +16700,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -16150,7 +16750,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -16200,7 +16800,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -16250,7 +16850,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -16300,7 +16900,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -16350,7 +16950,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -16400,7 +17000,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -16450,12 +17050,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -16500,12 +17100,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -16550,12 +17150,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -16600,12 +17200,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -16650,12 +17250,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -16700,12 +17300,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -16750,12 +17350,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -16800,12 +17400,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -16850,12 +17450,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -16900,7 +17500,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -16950,7 +17550,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -17000,7 +17600,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -17050,7 +17650,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -17100,7 +17700,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -17150,12 +17750,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -17200,66 +17800,62 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -17298,18 +17894,18 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -17354,12 +17950,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -17404,12 +18000,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -17454,12 +18050,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -17504,12 +18100,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -17554,12 +18150,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -17604,12 +18200,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -17654,7 +18250,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -17704,7 +18300,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -17714,47 +18310,51 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -17798,13 +18398,13 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -17854,12 +18454,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -17904,12 +18504,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -17954,12 +18554,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -18004,12 +18604,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -18054,12 +18654,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -18104,12 +18704,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -18154,12 +18754,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -18204,12 +18804,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -18254,12 +18854,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -18304,12 +18904,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -18354,12 +18954,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -18404,7 +19004,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -18454,7 +19054,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -18504,7 +19104,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -18548,6 +19148,606 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:45:18</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,12 +2402,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 21:45:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4702,12 +4702,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4752,12 +4752,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4802,12 +4802,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5452,12 +5452,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5502,12 +5502,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5552,12 +5552,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5752,7 +5752,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5852,7 +5852,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5902,7 +5902,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5952,7 +5952,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6052,7 +6052,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6152,12 +6152,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6202,12 +6202,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6252,12 +6252,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6352,12 +6352,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6402,12 +6402,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6452,7 +6452,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6462,51 +6462,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6550,13 +6546,13 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6606,7 +6602,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6656,7 +6652,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6706,7 +6702,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6756,7 +6752,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6766,47 +6762,51 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6850,13 +6850,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6906,12 +6906,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6956,12 +6956,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7006,12 +7006,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7106,12 +7106,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7156,12 +7156,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7206,12 +7206,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7306,7 +7306,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7356,7 +7356,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7406,7 +7406,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7456,7 +7456,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7506,7 +7506,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7706,12 +7706,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7756,12 +7756,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7856,12 +7856,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7906,12 +7906,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7956,12 +7956,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8006,12 +8006,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8056,7 +8056,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8156,7 +8156,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8256,7 +8256,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8356,7 +8356,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8406,12 +8406,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8456,12 +8456,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8506,12 +8506,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8556,12 +8556,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8606,12 +8606,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8656,12 +8656,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8706,12 +8706,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8756,12 +8756,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8806,12 +8806,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8856,7 +8856,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8906,7 +8906,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8956,7 +8956,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9006,7 +9006,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9106,7 +9106,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9156,12 +9156,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9206,66 +9206,62 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9304,18 +9300,18 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9360,12 +9356,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9410,12 +9406,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9460,12 +9456,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9510,12 +9506,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9560,12 +9556,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9610,12 +9606,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9660,7 +9656,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9710,7 +9706,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9720,47 +9716,51 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9804,13 +9804,13 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9910,12 +9910,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9960,12 +9960,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10010,12 +10010,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10060,12 +10060,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10110,12 +10110,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10160,12 +10160,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10210,12 +10210,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10260,12 +10260,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10310,12 +10310,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10360,12 +10360,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10410,12 +10410,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10460,7 +10460,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10560,7 +10560,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10610,7 +10610,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10654,6 +10654,606 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10668,7 +11268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11496,12 +12096,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 21:45:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11546,7 +12146,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11596,7 +12196,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11646,7 +12246,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11696,7 +12296,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11746,7 +12346,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11796,7 +12396,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11846,7 +12446,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11896,7 +12496,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11946,7 +12546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11996,7 +12596,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12046,7 +12646,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12096,7 +12696,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12146,7 +12746,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12196,7 +12796,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -12246,12 +12846,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12296,12 +12896,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12346,7 +12946,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12396,7 +12996,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12446,7 +13046,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12496,7 +13096,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12546,7 +13146,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12596,7 +13196,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12646,7 +13246,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12696,7 +13296,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12746,7 +13346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12796,7 +13396,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12846,7 +13446,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12896,7 +13496,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12946,7 +13546,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12996,12 +13596,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13046,12 +13646,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13096,12 +13696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13146,7 +13746,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13196,7 +13796,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13246,7 +13846,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13296,7 +13896,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13346,7 +13946,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13396,7 +13996,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -13446,7 +14046,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -13496,7 +14096,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13546,7 +14146,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13596,7 +14196,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13646,7 +14246,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13696,7 +14296,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13746,12 +14346,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -13796,12 +14396,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -13846,12 +14446,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -13896,12 +14496,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -13946,7 +14546,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13996,7 +14596,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -14046,7 +14646,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -14096,7 +14696,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -14146,7 +14746,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14196,7 +14796,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14246,7 +14846,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14296,7 +14896,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14346,7 +14946,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14396,7 +14996,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14446,7 +15046,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14496,12 +15096,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -14546,12 +15146,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -14596,12 +15196,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14646,12 +15246,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -14696,12 +15296,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -14746,7 +15346,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14796,7 +15396,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14846,7 +15446,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14896,7 +15496,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14946,7 +15546,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -14996,7 +15596,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -15046,7 +15646,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -15096,7 +15696,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -15146,7 +15746,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15196,7 +15796,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -15246,12 +15846,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -15296,12 +15896,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15346,12 +15946,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15396,12 +15996,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -15446,12 +16046,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15496,12 +16096,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -15546,7 +16146,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15556,51 +16156,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15644,13 +16240,13 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -15700,7 +16296,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -15750,7 +16346,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -15800,7 +16396,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -15850,7 +16446,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -15860,47 +16456,51 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -15944,13 +16544,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -16000,12 +16600,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -16050,12 +16650,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -16100,12 +16700,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -16150,12 +16750,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -16200,12 +16800,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -16250,12 +16850,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -16300,12 +16900,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -16350,7 +16950,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -16400,7 +17000,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -16450,7 +17050,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -16500,7 +17100,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -16550,7 +17150,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -16600,7 +17200,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -16650,7 +17250,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -16700,7 +17300,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -16750,12 +17350,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -16800,12 +17400,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -16850,12 +17450,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -16900,12 +17500,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -16950,12 +17550,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -17000,12 +17600,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -17050,12 +17650,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -17100,12 +17700,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -17150,7 +17750,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -17200,7 +17800,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -17250,7 +17850,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -17300,7 +17900,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -17350,7 +17950,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -17400,7 +18000,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -17450,7 +18050,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -17500,12 +18100,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -17550,12 +18150,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -17600,12 +18200,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -17650,12 +18250,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -17700,12 +18300,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -17750,12 +18350,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -17800,12 +18400,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -17850,12 +18450,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -17900,12 +18500,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -17950,7 +18550,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -18000,7 +18600,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -18050,7 +18650,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -18100,7 +18700,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -18150,7 +18750,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -18200,7 +18800,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -18250,12 +18850,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -18300,66 +18900,62 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -18398,18 +18994,18 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -18454,12 +19050,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -18504,12 +19100,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -18554,12 +19150,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -18604,12 +19200,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -18654,12 +19250,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -18704,12 +19300,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -18754,7 +19350,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -18804,7 +19400,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -18814,47 +19410,51 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -18898,13 +19498,13 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -18954,7 +19554,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -19004,12 +19604,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -19054,12 +19654,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -19104,12 +19704,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -19154,12 +19754,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -19204,12 +19804,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -19254,12 +19854,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -19304,12 +19904,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -19354,12 +19954,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -19404,12 +20004,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -19454,12 +20054,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -19504,12 +20104,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -19554,7 +20154,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -19604,7 +20204,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -19654,7 +20254,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -19704,7 +20304,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -19748,6 +20348,606 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:20:17</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,12 +2452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 22:19:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,12 +4852,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4952,12 +4952,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5002,12 +5002,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5452,7 +5452,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5652,12 +5652,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5702,12 +5702,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5752,12 +5752,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5802,12 +5802,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5852,12 +5852,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5902,7 +5902,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5952,7 +5952,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6052,7 +6052,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6152,7 +6152,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6252,7 +6252,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6352,7 +6352,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6402,7 +6402,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6452,12 +6452,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6502,12 +6502,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6552,12 +6552,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6602,12 +6602,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6652,12 +6652,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6702,12 +6702,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6762,51 +6762,47 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6850,13 +6846,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6906,7 +6902,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6956,7 +6952,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7006,7 +7002,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7052,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7066,47 +7062,51 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7150,13 +7150,13 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7306,12 +7306,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7356,12 +7356,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7506,12 +7506,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7556,12 +7556,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7656,7 +7656,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7706,7 +7706,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7806,7 +7806,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7856,7 +7856,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7906,7 +7906,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8056,12 +8056,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8106,12 +8106,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8156,12 +8156,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8206,12 +8206,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8256,12 +8256,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8356,12 +8356,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8406,12 +8406,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8506,7 +8506,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8556,7 +8556,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8656,7 +8656,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8706,7 +8706,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8756,7 +8756,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8856,12 +8856,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8906,12 +8906,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8956,12 +8956,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9006,12 +9006,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9056,12 +9056,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9106,12 +9106,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9156,12 +9156,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9206,12 +9206,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9256,12 +9256,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9406,7 +9406,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9456,7 +9456,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9506,7 +9506,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9556,7 +9556,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9606,7 +9606,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9656,12 +9656,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9706,66 +9706,62 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9804,18 +9800,18 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9860,12 +9856,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9910,12 +9906,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9960,12 +9956,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10010,12 +10006,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10060,12 +10056,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10110,12 +10106,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10160,7 +10156,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10210,7 +10206,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10220,47 +10216,51 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10304,13 +10304,13 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10360,7 +10360,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10410,7 +10410,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10460,12 +10460,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10510,12 +10510,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10560,12 +10560,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10610,12 +10610,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10660,12 +10660,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10710,12 +10710,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10760,12 +10760,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10810,12 +10810,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10860,12 +10860,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10910,12 +10910,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10960,12 +10960,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11010,7 +11010,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11110,7 +11110,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11160,7 +11160,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11210,7 +11210,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11254,6 +11254,606 @@
         <v>0</v>
       </c>
       <c r="N193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11268,7 +11868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12146,12 +12746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 22:19:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12196,7 +12796,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12246,7 +12846,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12296,7 +12896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12346,7 +12946,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12396,7 +12996,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12446,7 +13046,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12496,7 +13096,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12546,7 +13146,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12596,7 +13196,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12646,7 +13246,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12696,7 +13296,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12746,7 +13346,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12796,7 +13396,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -12846,7 +13446,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -12896,7 +13496,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12946,12 +13546,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12996,12 +13596,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13046,7 +13646,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -13096,7 +13696,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -13146,7 +13746,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -13196,7 +13796,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13246,7 +13846,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13296,7 +13896,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13346,7 +13946,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13396,7 +13996,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13446,7 +14046,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13496,7 +14096,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13546,7 +14146,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13596,7 +14196,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -13646,7 +14246,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -13696,7 +14296,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -13746,12 +14346,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13796,12 +14396,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13846,12 +14446,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13896,7 +14496,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13946,7 +14546,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13996,7 +14596,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14046,7 +14646,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14096,7 +14696,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14146,7 +14746,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -14196,7 +14796,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -14246,7 +14846,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -14296,7 +14896,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -14346,7 +14946,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -14396,7 +14996,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -14446,7 +15046,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -14496,7 +15096,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -14546,12 +15146,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -14596,12 +15196,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -14646,12 +15246,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -14696,12 +15296,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -14746,7 +15346,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14796,7 +15396,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14846,7 +15446,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14896,7 +15496,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14946,7 +15546,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14996,7 +15596,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -15046,7 +15646,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15096,7 +15696,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15146,7 +15746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15196,7 +15796,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15246,7 +15846,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -15296,7 +15896,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15346,12 +15946,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -15396,12 +15996,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -15446,12 +16046,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -15496,12 +16096,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15546,12 +16146,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15596,7 +16196,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -15646,7 +16246,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -15696,7 +16296,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -15746,7 +16346,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15796,7 +16396,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -15846,7 +16446,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -15896,7 +16496,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -15946,7 +16546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15996,7 +16596,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -16046,7 +16646,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -16096,7 +16696,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -16146,12 +16746,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -16196,12 +16796,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -16246,12 +16846,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -16296,12 +16896,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -16346,12 +16946,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -16396,12 +16996,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -16446,7 +17046,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -16456,51 +17056,47 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -16544,13 +17140,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -16600,7 +17196,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -16650,7 +17246,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -16700,7 +17296,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -16750,7 +17346,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -16760,47 +17356,51 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -16844,13 +17444,13 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -16900,7 +17500,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -16950,12 +17550,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -17000,12 +17600,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -17050,12 +17650,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -17100,12 +17700,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -17150,12 +17750,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -17200,12 +17800,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -17250,12 +17850,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -17300,7 +17900,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -17350,7 +17950,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -17400,7 +18000,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -17450,7 +18050,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -17500,7 +18100,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -17550,7 +18150,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -17600,7 +18200,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -17650,7 +18250,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -17700,7 +18300,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -17750,12 +18350,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -17800,12 +18400,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -17850,12 +18450,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -17900,12 +18500,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -17950,12 +18550,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -18000,12 +18600,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -18050,12 +18650,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -18100,12 +18700,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -18150,7 +18750,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -18200,7 +18800,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -18250,7 +18850,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -18300,7 +18900,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -18350,7 +18950,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -18400,7 +19000,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -18450,7 +19050,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -18500,7 +19100,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -18550,12 +19150,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -18600,12 +19200,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -18650,12 +19250,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -18700,12 +19300,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -18750,12 +19350,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -18800,12 +19400,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -18850,12 +19450,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -18900,12 +19500,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -18950,12 +19550,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -19000,7 +19600,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -19050,7 +19650,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -19100,7 +19700,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -19150,7 +19750,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -19200,7 +19800,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -19250,7 +19850,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -19300,7 +19900,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -19350,12 +19950,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -19400,66 +20000,62 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -19498,18 +20094,18 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -19554,12 +20150,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -19604,12 +20200,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -19654,12 +20250,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -19704,12 +20300,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -19754,12 +20350,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -19804,12 +20400,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -19854,7 +20450,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19904,7 +20500,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19914,47 +20510,51 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -19998,13 +20598,13 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -20054,7 +20654,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -20104,7 +20704,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -20154,12 +20754,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -20204,12 +20804,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -20254,12 +20854,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -20304,12 +20904,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -20354,12 +20954,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -20404,12 +21004,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -20454,12 +21054,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -20504,12 +21104,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -20554,12 +21154,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -20604,12 +21204,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -20654,12 +21254,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -20704,7 +21304,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -20754,7 +21354,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -20804,7 +21404,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -20854,7 +21454,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -20904,7 +21504,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -20948,6 +21548,606 @@
         <v>0</v>
       </c>
       <c r="N193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:45:48</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N205"/>
+  <dimension ref="A1:N217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2502,12 +2502,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 22:46:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2552,7 +2552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:28</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,12 +3402,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 22:46:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,7 +4052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:17</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4252,12 +4252,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 22:46:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:12</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5052,12 +5052,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5102,12 +5102,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5202,12 +5202,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 22:45:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5452,7 +5452,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5752,7 +5752,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5852,7 +5852,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:14</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5902,12 +5902,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5952,12 +5952,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6002,12 +6002,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6052,12 +6052,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6102,12 +6102,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 22:45:59</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6152,7 +6152,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6252,7 +6252,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6352,7 +6352,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6402,7 +6402,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6452,7 +6452,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6552,7 +6552,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6602,7 +6602,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6652,7 +6652,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6752,12 +6752,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,12 +6802,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6852,12 +6852,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6902,12 +6902,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6952,12 +6952,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7002,12 +7002,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 22:46:11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7052,7 +7052,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7062,51 +7062,47 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7150,13 +7146,13 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7206,7 +7202,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7256,7 +7252,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7306,7 +7302,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7356,7 +7352,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7366,47 +7362,51 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7450,13 +7450,13 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7506,7 +7506,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:25</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7706,12 +7706,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7756,12 +7756,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7856,12 +7856,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7906,12 +7906,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 22:46:10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8056,7 +8056,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8156,7 +8156,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8256,7 +8256,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8356,7 +8356,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:18</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8456,12 +8456,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8506,12 +8506,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8556,12 +8556,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8606,12 +8606,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8656,12 +8656,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8706,12 +8706,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8756,12 +8756,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8806,12 +8806,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 22:46:04</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8856,7 +8856,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8906,7 +8906,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8956,7 +8956,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9006,7 +9006,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9106,7 +9106,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9156,7 +9156,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9206,7 +9206,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9256,7 +9256,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:20</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9306,12 +9306,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9356,12 +9356,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9406,12 +9406,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9456,12 +9456,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9506,12 +9506,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9556,12 +9556,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9606,12 +9606,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9656,12 +9656,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9706,12 +9706,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 22:46:05</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9756,7 +9756,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9806,7 +9806,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9856,7 +9856,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9956,7 +9956,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10056,7 +10056,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10106,7 +10106,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10156,12 +10156,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10206,66 +10206,62 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10304,18 +10300,18 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10360,12 +10356,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10410,12 +10406,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10460,12 +10456,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10510,12 +10506,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10560,12 +10556,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10610,12 +10606,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 22:46:14</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10660,7 +10656,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10710,7 +10706,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10720,47 +10716,51 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10804,13 +10804,13 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10860,7 +10860,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:23</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11010,12 +11010,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11060,12 +11060,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11110,12 +11110,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11160,12 +11160,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11210,12 +11210,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11260,12 +11260,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11310,12 +11310,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11360,12 +11360,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11410,12 +11410,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11460,12 +11460,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11510,12 +11510,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 22:46:08</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11560,7 +11560,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11610,7 +11610,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11660,7 +11660,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11760,7 +11760,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:15</t>
+          <t>2026-09-18 16:45:48</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11854,6 +11854,606 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:46:01</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11868,7 +12468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N205"/>
+  <dimension ref="A1:N217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12796,12 +13396,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 22:46:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12846,7 +13446,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12896,7 +13496,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12946,7 +13546,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12996,7 +13596,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13046,7 +13646,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13096,7 +13696,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13146,7 +13746,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13196,7 +13796,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13246,7 +13846,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13296,7 +13896,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13346,7 +13946,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13396,7 +13996,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13446,7 +14046,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13496,7 +14096,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13546,7 +14146,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -13596,7 +14196,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:28</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -13646,12 +14246,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13696,12 +14296,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 22:46:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13746,7 +14346,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -13796,7 +14396,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13846,7 +14446,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13896,7 +14496,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13946,7 +14546,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13996,7 +14596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14046,7 +14646,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14096,7 +14696,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14146,7 +14746,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14196,7 +14796,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14246,7 +14846,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14296,7 +14896,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14346,7 +14946,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -14396,7 +14996,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -14446,7 +15046,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:17</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14496,12 +15096,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14546,12 +15146,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14596,12 +15196,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 22:46:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14646,7 +15246,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14696,7 +15296,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14746,7 +15346,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -14796,7 +15396,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -14846,7 +15446,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -14896,7 +15496,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -14946,7 +15546,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -14996,7 +15596,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15046,7 +15646,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15096,7 +15696,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -15146,7 +15746,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -15196,7 +15796,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -15246,7 +15846,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -15296,7 +15896,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:12</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -15346,12 +15946,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15396,12 +15996,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15446,12 +16046,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15496,12 +16096,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 22:45:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15546,7 +16146,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -15596,7 +16196,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -15646,7 +16246,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15696,7 +16296,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15746,7 +16346,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15796,7 +16396,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15846,7 +16446,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -15896,7 +16496,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15946,7 +16546,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -15996,7 +16596,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16046,7 +16646,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -16096,7 +16696,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16146,7 +16746,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:14</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16196,12 +16796,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16246,12 +16846,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -16296,12 +16896,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -16346,12 +16946,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16396,12 +16996,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 22:45:59</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16446,7 +17046,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -16496,7 +17096,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -16546,7 +17146,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -16596,7 +17196,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -16646,7 +17246,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -16696,7 +17296,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -16746,7 +17346,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -16796,7 +17396,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -16846,7 +17446,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -16896,7 +17496,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -16946,7 +17546,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -16996,7 +17596,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -17046,12 +17646,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -17096,12 +17696,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -17146,12 +17746,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -17196,12 +17796,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -17246,12 +17846,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -17296,12 +17896,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 22:46:11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -17346,7 +17946,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -17356,51 +17956,47 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -17444,13 +18040,13 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -17500,7 +18096,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -17550,7 +18146,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -17600,7 +18196,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -17650,7 +18246,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -17660,47 +18256,51 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -17744,13 +18344,13 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -17800,7 +18400,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -17850,7 +18450,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:25</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -17900,12 +18500,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -17950,12 +18550,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -18000,12 +18600,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -18050,12 +18650,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -18100,12 +18700,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -18150,12 +18750,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -18200,12 +18800,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 22:46:10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -18250,7 +18850,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -18300,7 +18900,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -18350,7 +18950,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -18400,7 +19000,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -18450,7 +19050,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -18500,7 +19100,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -18550,7 +19150,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -18600,7 +19200,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -18650,7 +19250,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -18700,7 +19300,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:18</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -18750,12 +19350,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -18800,12 +19400,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -18850,12 +19450,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -18900,12 +19500,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -18950,12 +19550,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -19000,12 +19600,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -19050,12 +19650,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -19100,12 +19700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 22:46:04</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -19150,7 +19750,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -19200,7 +19800,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -19250,7 +19850,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -19300,7 +19900,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -19350,7 +19950,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -19400,7 +20000,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -19450,7 +20050,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -19500,7 +20100,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -19550,7 +20150,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:20</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -19600,12 +20200,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -19650,12 +20250,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -19700,12 +20300,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -19750,12 +20350,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -19800,12 +20400,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -19850,12 +20450,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -19900,12 +20500,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -19950,12 +20550,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -20000,12 +20600,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 22:46:05</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -20050,7 +20650,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -20100,7 +20700,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -20150,7 +20750,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -20200,7 +20800,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -20250,7 +20850,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -20300,7 +20900,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -20350,7 +20950,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -20400,7 +21000,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -20450,12 +21050,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -20500,66 +21100,62 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -20598,18 +21194,18 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -20654,12 +21250,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -20704,12 +21300,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20754,12 +21350,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -20804,12 +21400,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -20854,12 +21450,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -20904,12 +21500,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 22:46:14</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -20954,7 +21550,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -21004,7 +21600,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -21014,47 +21610,51 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -21098,13 +21698,13 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -21154,7 +21754,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -21204,7 +21804,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -21254,7 +21854,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:23</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -21304,12 +21904,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -21354,12 +21954,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -21404,12 +22004,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -21454,12 +22054,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -21504,12 +22104,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -21554,12 +22154,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -21604,12 +22204,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -21654,12 +22254,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -21704,12 +22304,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -21754,12 +22354,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -21804,12 +22404,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 22:46:08</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -21854,7 +22454,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -21904,7 +22504,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -21954,7 +22554,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -22004,7 +22604,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -22054,7 +22654,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -22104,7 +22704,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:15</t>
+          <t>2026-09-18 16:45:48</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -22148,6 +22748,606 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:18:59</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:46:01</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -746,23 +746,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Roseate丨杨博文</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-13 20:48:29</t>
+        </is>
+      </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -774,42 +778,42 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>32.21%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20.08%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29.55%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11.72%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>91.74%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>78.6:1</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N217"/>
+  <dimension ref="A1:N229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,12 +2556,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 23:18:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2602,7 +2606,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2652,7 +2656,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2702,7 +2706,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2752,7 +2756,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2802,7 +2806,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2852,7 +2856,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2902,7 +2906,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2952,7 +2956,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3002,7 +3006,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3056,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,7 +3106,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,7 +3156,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3202,7 +3206,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3252,7 +3256,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,7 +3306,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3352,7 +3356,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:28</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3402,7 +3406,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:13</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,12 +3456,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 22:46:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3502,57 +3506,61 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 23:18:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-08-13 20:48:29</t>
+        </is>
+      </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>12221</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>11212</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>7619</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>4447</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3602,7 +3610,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,7 +3660,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3702,7 +3710,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3752,7 +3760,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3802,7 +3810,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3852,7 +3860,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3902,7 +3910,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3952,7 +3960,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,7 +4010,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4052,7 +4060,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4102,7 +4110,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4152,7 +4160,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4202,7 +4210,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4252,7 +4260,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:17</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4302,7 +4310,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:02</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4352,12 +4360,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4402,12 +4410,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 22:46:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4452,12 +4460,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 23:18:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4502,7 +4510,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4552,7 +4560,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4602,7 +4610,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4652,7 +4660,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4702,7 +4710,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4752,7 +4760,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4802,7 +4810,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4852,7 +4860,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4902,7 +4910,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4952,7 +4960,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5002,7 +5010,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5052,7 +5060,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5102,7 +5110,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5152,7 +5160,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:12</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5202,7 +5210,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:57</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5252,12 +5260,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5302,12 +5310,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5352,12 +5360,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 22:45:57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5402,12 +5410,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 23:18:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5452,7 +5460,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5502,7 +5510,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5552,7 +5560,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5602,7 +5610,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5652,7 +5660,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5702,7 +5710,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5752,7 +5760,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5802,7 +5810,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5852,7 +5860,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5902,7 +5910,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5952,7 +5960,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6002,7 +6010,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6052,7 +6060,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:14</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6102,7 +6110,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:59</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6152,12 +6160,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6202,12 +6210,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6252,12 +6260,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6302,12 +6310,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 22:45:59</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6352,12 +6360,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 23:18:36</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6402,7 +6410,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6452,7 +6460,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6502,7 +6510,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6552,7 +6560,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6602,7 +6610,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6652,7 +6660,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6702,7 +6710,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6752,7 +6760,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6802,7 +6810,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6852,7 +6860,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6902,7 +6910,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6952,7 +6960,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7002,7 +7010,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:11</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7052,12 +7060,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7102,12 +7110,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7152,12 +7160,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7202,12 +7210,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7252,12 +7260,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 22:46:11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7302,12 +7310,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 23:18:48</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7352,7 +7360,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7362,51 +7370,47 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7450,13 +7454,13 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7506,7 +7510,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7556,7 +7560,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7606,7 +7610,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7656,7 +7660,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7666,47 +7670,51 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7750,13 +7758,13 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7806,7 +7814,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7856,7 +7864,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:25</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7906,7 +7914,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:10</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7956,12 +7964,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8006,12 +8014,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8056,12 +8064,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8106,12 +8114,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8156,12 +8164,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8206,12 +8214,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 22:46:10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8256,12 +8264,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 23:18:46</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8306,7 +8314,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8356,7 +8364,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8406,7 +8414,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8456,7 +8464,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8506,7 +8514,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8556,7 +8564,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8606,7 +8614,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8656,7 +8664,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8706,7 +8714,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8756,7 +8764,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:18</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8806,7 +8814,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:04</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8856,12 +8864,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8906,12 +8914,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8956,12 +8964,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9006,12 +9014,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9056,12 +9064,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9106,12 +9114,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9156,12 +9164,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 22:46:04</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9206,12 +9214,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 23:18:40</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9256,7 +9264,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9306,7 +9314,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9356,7 +9364,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9406,7 +9414,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9456,7 +9464,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9506,7 +9514,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9556,7 +9564,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9606,7 +9614,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9656,7 +9664,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:20</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9706,7 +9714,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:05</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9756,12 +9764,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9806,12 +9814,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9856,12 +9864,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9906,12 +9914,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9956,12 +9964,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10006,12 +10014,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10056,12 +10064,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10106,12 +10114,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 22:46:05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10156,12 +10164,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 23:18:42</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10206,7 +10214,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10256,7 +10264,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10306,7 +10314,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10356,7 +10364,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10406,7 +10414,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10456,7 +10464,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10506,7 +10514,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10556,7 +10564,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10606,7 +10614,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:14</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10656,12 +10664,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10706,66 +10714,62 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10804,18 +10808,18 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10860,12 +10864,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10910,12 +10914,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10960,12 +10964,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11010,12 +11014,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11060,12 +11064,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 22:46:14</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11110,12 +11114,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 23:18:51</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11160,7 +11164,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11210,7 +11214,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11220,47 +11224,51 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11304,13 +11312,13 @@
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11360,7 +11368,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11410,7 +11418,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11460,7 +11468,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:23</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11510,7 +11518,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:08</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11560,12 +11568,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11610,12 +11618,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11660,12 +11668,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11710,12 +11718,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11760,12 +11768,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11810,12 +11818,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11860,12 +11868,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11910,12 +11918,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11960,12 +11968,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12010,12 +12018,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 22:46:08</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12060,12 +12068,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 23:18:45</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12110,7 +12118,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12160,7 +12168,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12210,7 +12218,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12260,7 +12268,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12310,7 +12318,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12360,7 +12368,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:15</t>
+          <t>2026-09-18 16:45:48</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12410,7 +12418,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:01</t>
+          <t>2026-09-18 17:18:59</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12454,6 +12462,606 @@
         <v>0</v>
       </c>
       <c r="N217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:46:01</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:18:37</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12468,7 +13076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N217"/>
+  <dimension ref="A1:N229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13446,12 +14054,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 23:18:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13496,7 +14104,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13546,7 +14154,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13596,7 +14204,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13646,7 +14254,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13696,7 +14304,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13746,7 +14354,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13796,7 +14404,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13846,7 +14454,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13896,7 +14504,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13946,7 +14554,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13996,7 +14604,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14046,7 +14654,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14096,7 +14704,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14146,7 +14754,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14196,7 +14804,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14246,7 +14854,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:28</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14296,7 +14904,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:13</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14346,12 +14954,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 22:46:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14396,57 +15004,61 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 23:18:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-08-13 20:48:29</t>
+        </is>
+      </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>12221</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>11212</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>7619</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>4447</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14496,7 +15108,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14546,7 +15158,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14596,7 +15208,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14646,7 +15258,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14696,7 +15308,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14746,7 +15358,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14796,7 +15408,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14846,7 +15458,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14896,7 +15508,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14946,7 +15558,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -14996,7 +15608,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -15046,7 +15658,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -15096,7 +15708,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -15146,7 +15758,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:17</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -15196,7 +15808,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:02</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -15246,12 +15858,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15296,12 +15908,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 22:46:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15346,12 +15958,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 23:18:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15396,7 +16008,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15446,7 +16058,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15496,7 +16108,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15546,7 +16158,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15596,7 +16208,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15646,7 +16258,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15696,7 +16308,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -15746,7 +16358,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -15796,7 +16408,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -15846,7 +16458,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -15896,7 +16508,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -15946,7 +16558,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -15996,7 +16608,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16046,7 +16658,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:12</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -16096,7 +16708,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:57</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -16146,12 +16758,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -16196,12 +16808,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -16246,12 +16858,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 22:45:57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -16296,12 +16908,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 23:18:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16346,7 +16958,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -16396,7 +17008,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -16446,7 +17058,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -16496,7 +17108,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -16546,7 +17158,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16596,7 +17208,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16646,7 +17258,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -16696,7 +17308,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16746,7 +17358,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16796,7 +17408,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -16846,7 +17458,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -16896,7 +17508,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -16946,7 +17558,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:14</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -16996,7 +17608,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:59</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -17046,12 +17658,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -17096,12 +17708,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -17146,12 +17758,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -17196,12 +17808,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 22:45:59</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -17246,12 +17858,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 23:18:36</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17296,7 +17908,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -17346,7 +17958,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -17396,7 +18008,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -17446,7 +18058,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -17496,7 +18108,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -17546,7 +18158,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -17596,7 +18208,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -17646,7 +18258,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -17696,7 +18308,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -17746,7 +18358,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -17796,7 +18408,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -17846,7 +18458,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -17896,7 +18508,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:11</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -17946,12 +18558,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -17996,12 +18608,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -18046,12 +18658,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -18096,12 +18708,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -18146,12 +18758,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 22:46:11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -18196,12 +18808,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 23:18:48</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -18246,7 +18858,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -18256,51 +18868,47 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -18344,13 +18952,13 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -18400,7 +19008,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -18450,7 +19058,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -18500,7 +19108,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -18550,7 +19158,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -18560,47 +19168,51 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -18644,13 +19256,13 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -18700,7 +19312,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -18750,7 +19362,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:25</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -18800,7 +19412,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:10</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -18850,12 +19462,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -18900,12 +19512,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -18950,12 +19562,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -19000,12 +19612,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -19050,12 +19662,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -19100,12 +19712,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 22:46:10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -19150,12 +19762,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 23:18:46</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -19200,7 +19812,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -19250,7 +19862,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -19300,7 +19912,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -19350,7 +19962,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -19400,7 +20012,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -19450,7 +20062,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -19500,7 +20112,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -19550,7 +20162,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -19600,7 +20212,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -19650,7 +20262,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:18</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -19700,7 +20312,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:04</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -19750,12 +20362,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -19800,12 +20412,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -19850,12 +20462,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -19900,12 +20512,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -19950,12 +20562,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -20000,12 +20612,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -20050,12 +20662,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 22:46:04</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -20100,12 +20712,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 23:18:40</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -20150,7 +20762,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -20200,7 +20812,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -20250,7 +20862,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -20300,7 +20912,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -20350,7 +20962,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -20400,7 +21012,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -20450,7 +21062,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -20500,7 +21112,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -20550,7 +21162,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:20</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -20600,7 +21212,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:05</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -20650,12 +21262,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -20700,12 +21312,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:32</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -20750,12 +21362,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:35</t>
+          <t>2026-09-18 20:23:16</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -20800,12 +21412,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:32</t>
+          <t>2026-09-18 20:49:22</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -20850,12 +21462,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:31</t>
+          <t>2026-09-18 21:18:31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -20900,12 +21512,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:01</t>
+          <t>2026-09-18 21:45:30</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -20950,12 +21562,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:13</t>
+          <t>2026-09-18 22:19:20</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -21000,12 +21612,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:04</t>
+          <t>2026-09-18 22:46:05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -21050,12 +21662,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:43</t>
+          <t>2026-09-18 23:18:42</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -21100,7 +21712,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:16</t>
+          <t>2026-09-18 14:24:28</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -21150,7 +21762,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:30</t>
+          <t>2026-09-18 14:49:32</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -21200,7 +21812,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:23</t>
+          <t>2026-09-18 15:19:35</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -21250,7 +21862,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:25</t>
+          <t>2026-09-18 15:45:32</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -21300,7 +21912,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:31</t>
+          <t>2026-09-18 16:20:31</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -21350,7 +21962,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:40</t>
+          <t>2026-09-18 16:46:01</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -21400,7 +22012,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:40</t>
+          <t>2026-09-18 17:19:13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -21450,7 +22062,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:29</t>
+          <t>2026-09-18 17:45:04</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -21500,7 +22112,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:14</t>
+          <t>2026-09-18 18:19:43</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -21550,12 +22162,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:22</t>
+          <t>2026-09-18 18:45:16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -21600,66 +22212,62 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:26</t>
+          <t>2026-09-18 19:18:30</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>【杨博文｜4k直拍】100Ways 直拍</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>关键时刻来瓶尖叫</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2026-08-14 01:41:46</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>4449</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>3318</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:29</t>
+          <t>2026-09-18 19:44:23</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -21698,18 +22306,18 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>-181043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:26</t>
+          <t>2026-09-18 20:23:25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -21754,12 +22362,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:25</t>
+          <t>2026-09-18 20:49:31</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -21804,12 +22412,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:55</t>
+          <t>2026-09-18 21:18:40</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -21854,12 +22462,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:07</t>
+          <t>2026-09-18 21:45:40</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -21904,12 +22512,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:58</t>
+          <t>2026-09-18 22:19:29</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -21954,12 +22562,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:37</t>
+          <t>2026-09-18 22:46:14</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -22004,12 +22612,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:10</t>
+          <t>2026-09-18 23:18:51</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BV1rqgW6hEvv</t>
+          <t>BV1r8eV6fE5N</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -22054,7 +22662,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:24</t>
+          <t>2026-09-18 14:24:22</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -22104,7 +22712,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:17</t>
+          <t>2026-09-18 14:49:26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -22114,47 +22722,51 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文｜4k直拍】100Ways 直拍</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
+          <t>关键时刻来瓶尖叫</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-08-14 01:41:46</t>
+        </is>
+      </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>4449</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>181043</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:19</t>
+          <t>2026-09-18 15:19:29</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -22198,13 +22810,13 @@
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>-181043</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:25</t>
+          <t>2026-09-18 15:45:26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -22254,7 +22866,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:34</t>
+          <t>2026-09-18 16:20:25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -22304,7 +22916,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:34</t>
+          <t>2026-09-18 16:45:55</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -22354,7 +22966,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:23</t>
+          <t>2026-09-18 17:19:07</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -22404,7 +23016,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:08</t>
+          <t>2026-09-18 17:44:58</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -22454,12 +23066,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:15</t>
+          <t>2026-09-18 18:19:37</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -22504,12 +23116,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:18</t>
+          <t>2026-09-18 18:45:10</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -22554,12 +23166,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:21</t>
+          <t>2026-09-18 19:18:24</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -22604,12 +23216,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:18</t>
+          <t>2026-09-18 19:44:17</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -22654,12 +23266,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:17</t>
+          <t>2026-09-18 20:23:19</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -22704,12 +23316,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:48</t>
+          <t>2026-09-18 20:49:25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -22754,12 +23366,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:59</t>
+          <t>2026-09-18 21:18:34</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -22804,12 +23416,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:51</t>
+          <t>2026-09-18 21:45:34</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -22854,12 +23466,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:30</t>
+          <t>2026-09-18 22:19:23</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -22904,12 +23516,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:02</t>
+          <t>2026-09-18 22:46:08</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -22954,12 +23566,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:17</t>
+          <t>2026-09-18 23:18:45</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BV1xebR6zEkr</t>
+          <t>BV1rqgW6hEvv</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -23004,7 +23616,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:09</t>
+          <t>2026-09-18 14:24:15</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -23054,7 +23666,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:11</t>
+          <t>2026-09-18 14:49:18</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -23104,7 +23716,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:17</t>
+          <t>2026-09-18 15:19:21</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -23154,7 +23766,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:26</t>
+          <t>2026-09-18 15:45:18</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -23204,7 +23816,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:26</t>
+          <t>2026-09-18 16:20:17</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -23254,7 +23866,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:15</t>
+          <t>2026-09-18 16:45:48</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -23304,7 +23916,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:01</t>
+          <t>2026-09-18 17:18:59</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -23348,6 +23960,606 @@
         <v>0</v>
       </c>
       <c r="N217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:44:51</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:19:30</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45:02</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:18:17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:44:09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:23:11</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:49:17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:18:26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:45:26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:19:15</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:46:01</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:18:37</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BV1xebR6zEkr</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bilibili_20260918_report.xlsx
+++ b/bilibili_20260918_report.xlsx
@@ -746,27 +746,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-13 20:48:29</t>
-        </is>
-      </c>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>37947</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>37947</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -778,42 +774,42 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20.08%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29.55%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>11.72%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>91.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>78.6:1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N229"/>
+  <dimension ref="A1:N241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2606,12 +2602,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-18 23:45:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV18ZgH6uEYv</t>
+          <t>BV15egs6pEJp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2656,7 +2652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:31</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2706,7 +2702,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:34</t>
+          <t>2026-09-18 14:49:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2756,7 +2752,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:30</t>
+          <t>2026-09-18 15:19:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2806,7 +2802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:30</t>
+          <t>2026-09-18 15:45:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2856,7 +2852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 16:46:00</t>
+          <t>2026-09-18 16:20:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2906,7 +2902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:11</t>
+          <t>2026-09-18 16:46:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2956,7 +2952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:03</t>
+          <t>2026-09-18 17:19:11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3002,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:42</t>
+          <t>2026-09-18 17:45:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3056,7 +3052,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:14</t>
+          <t>2026-09-18 18:19:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3106,7 +3102,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:28</t>
+          <t>2026-09-18 18:45:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3156,7 +3152,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:21</t>
+          <t>2026-09-18 19:18:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3206,7 +3202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:23</t>
+          <t>2026-09-18 19:44:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3256,7 +3252,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:30</t>
+          <t>2026-09-18 20:23:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3306,7 +3302,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:39</t>
+          <t>2026-09-18 20:49:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3356,7 +3352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:38</t>
+          <t>2026-09-18 21:18:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3406,7 +3402,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:28</t>
+          <t>2026-09-18 21:45:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3456,7 +3452,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:13</t>
+          <t>2026-09-18 22:19:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3506,7 +3502,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:49</t>
+          <t>2026-09-18 22:46:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3516,106 +3512,106 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Roseate丨杨博文</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-08-13 20:48:29</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>37947</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>12221</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>11212</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>7619</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>4447</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>37947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:16</t>
+          <t>2026-09-18 23:18:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>【杨博文】&lt;100Ways&gt;4k两天混剪竖版直拍Focus</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Roseate丨杨博文</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-08-13 20:48:29</t>
+        </is>
+      </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>12221</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>11212</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>7619</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>4447</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>37947</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:20</t>
+          <t>2026-09-18 23:45:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV1E2bR6hEJR</t>
+          <t>BV18ZgH6uEYv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3654,13 +3650,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>-37947</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:23</t>
+          <t>2026-09-18 14:24:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,7 +3706,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:19</t>
+          <t>2026-09-18 14:49:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3760,7 +3756,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:19</t>
+          <t>2026-09-18 15:19:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3810,7 +3806,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:49</t>
+          <t>2026-09-18 15:45:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3860,7 +3856,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:00</t>
+          <t>2026-09-18 16:20:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3910,7 +3906,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:52</t>
+          <t>2026-09-18 16:45:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3960,7 +3956,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:31</t>
+          <t>2026-09-18 17:19:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4010,7 +4006,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:03</t>
+          <t>2026-09-18 17:44:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4060,7 +4056,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:18</t>
+          <t>2026-09-18 18:19:31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4110,7 +4106,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:10</t>
+          <t>2026-09-18 18:45:03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4160,7 +4156,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:12</t>
+          <t>2026-09-18 19:18:18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4210,7 +4206,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:19</t>
+          <t>2026-09-18 19:44:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4260,7 +4256,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:28</t>
+          <t>2026-09-18 20:23:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4310,7 +4306,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:27</t>
+          <t>2026-09-18 20:49:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4360,7 +4356,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:17</t>
+          <t>2026-09-18 21:18:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4410,7 +4406,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:02</t>
+          <t>2026-09-18 21:45:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4460,7 +4456,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:39</t>
+          <t>2026-09-18 22:19:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4510,12 +4506,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:12</t>
+          <t>2026-09-18 22:46:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4560,12 +4556,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:15</t>
+          <t>2026-09-18 23:18:39</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4610,12 +4606,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:18</t>
+          <t>2026-09-18 23:45:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV1GdgW6JEe9</t>
+          <t>BV1E2bR6hEJR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4660,7 +4656,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:15</t>
+          <t>2026-09-18 14:24:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4710,7 +4706,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:14</t>
+          <t>2026-09-18 14:49:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4760,7 +4756,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:45</t>
+          <t>2026-09-18 15:19:18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4810,7 +4806,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:55</t>
+          <t>2026-09-18 15:45:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4860,7 +4856,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:47</t>
+          <t>2026-09-18 16:20:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4910,7 +4906,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:27</t>
+          <t>2026-09-18 16:45:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4960,7 +4956,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18 18:44:59</t>
+          <t>2026-09-18 17:18:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5010,7 +5006,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:13</t>
+          <t>2026-09-18 17:44:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5060,7 +5056,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:06</t>
+          <t>2026-09-18 18:19:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5110,7 +5106,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:08</t>
+          <t>2026-09-18 18:44:59</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5160,7 +5156,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:14</t>
+          <t>2026-09-18 19:18:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5210,7 +5206,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:23</t>
+          <t>2026-09-18 19:44:06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5260,7 +5256,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:23</t>
+          <t>2026-09-18 20:23:08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5310,7 +5306,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:12</t>
+          <t>2026-09-18 20:49:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5360,7 +5356,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:57</t>
+          <t>2026-09-18 21:18:23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5410,7 +5406,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:34</t>
+          <t>2026-09-18 21:45:23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5460,12 +5456,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:13</t>
+          <t>2026-09-18 22:19:12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5510,12 +5506,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:17</t>
+          <t>2026-09-18 22:45:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5560,12 +5556,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:19</t>
+          <t>2026-09-18 23:18:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5610,12 +5606,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:16</t>
+          <t>2026-09-18 23:45:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV1W5gs6KEhr</t>
+          <t>BV1GdgW6JEe9</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5660,7 +5656,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:15</t>
+          <t>2026-09-18 14:24:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5710,7 +5706,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:46</t>
+          <t>2026-09-18 14:49:17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5760,7 +5756,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18 17:18:57</t>
+          <t>2026-09-18 15:19:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5810,7 +5806,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:49</t>
+          <t>2026-09-18 15:45:16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5860,7 +5856,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:29</t>
+          <t>2026-09-18 16:20:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5910,7 +5906,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:00</t>
+          <t>2026-09-18 16:45:46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5960,7 +5956,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:15</t>
+          <t>2026-09-18 17:18:57</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6010,7 +6006,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:07</t>
+          <t>2026-09-18 17:44:49</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6060,7 +6056,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:09</t>
+          <t>2026-09-18 18:19:29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6110,7 +6106,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:16</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6160,7 +6156,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:25</t>
+          <t>2026-09-18 19:18:15</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6210,7 +6206,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:24</t>
+          <t>2026-09-18 19:44:07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6260,7 +6256,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:14</t>
+          <t>2026-09-18 20:23:09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6310,7 +6306,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18 22:45:59</t>
+          <t>2026-09-18 20:49:16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6360,7 +6356,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:36</t>
+          <t>2026-09-18 21:18:25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6410,12 +6406,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:25</t>
+          <t>2026-09-18 21:45:24</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6460,12 +6456,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:29</t>
+          <t>2026-09-18 22:19:14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6510,12 +6506,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:32</t>
+          <t>2026-09-18 22:45:59</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6560,12 +6556,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:29</t>
+          <t>2026-09-18 23:18:36</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6610,12 +6606,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:28</t>
+          <t>2026-09-18 23:45:14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV1c3gF6wERf</t>
+          <t>BV1W5gs6KEhr</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6660,7 +6656,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:58</t>
+          <t>2026-09-18 14:24:25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6710,7 +6706,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:10</t>
+          <t>2026-09-18 14:49:29</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6760,7 +6756,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:01</t>
+          <t>2026-09-18 15:19:32</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6810,7 +6806,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:40</t>
+          <t>2026-09-18 15:45:29</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6860,7 +6856,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:13</t>
+          <t>2026-09-18 16:20:28</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6910,7 +6906,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:27</t>
+          <t>2026-09-18 16:45:58</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6960,7 +6956,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:20</t>
+          <t>2026-09-18 17:19:10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7010,7 +7006,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:22</t>
+          <t>2026-09-18 17:45:01</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,7 +7056,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:28</t>
+          <t>2026-09-18 18:19:40</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7110,7 +7106,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:37</t>
+          <t>2026-09-18 18:45:13</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7160,7 +7156,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:37</t>
+          <t>2026-09-18 19:18:27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7210,7 +7206,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:26</t>
+          <t>2026-09-18 19:44:20</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7260,7 +7256,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:11</t>
+          <t>2026-09-18 20:23:22</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7310,7 +7306,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:48</t>
+          <t>2026-09-18 20:49:28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7360,12 +7356,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:24</t>
+          <t>2026-09-18 21:18:37</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7410,12 +7406,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:28</t>
+          <t>2026-09-18 21:45:37</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7460,12 +7456,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:30</t>
+          <t>2026-09-18 22:19:26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7510,12 +7506,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:27</t>
+          <t>2026-09-18 22:46:11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7560,12 +7556,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:26</t>
+          <t>2026-09-18 23:18:48</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7610,12 +7606,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:57</t>
+          <t>2026-09-18 23:45:27</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV1k9gw6gE4U</t>
+          <t>BV1c3gF6wERf</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7660,7 +7656,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:08</t>
+          <t>2026-09-18 14:24:24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7670,51 +7666,47 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
+          <t>获取失败</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Astra_杨博文</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:49:20</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>3042</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18 17:45:00</t>
+          <t>2026-09-18 14:49:28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7758,13 +7750,13 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>-143345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:39</t>
+          <t>2026-09-18 15:19:30</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7814,7 +7806,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:11</t>
+          <t>2026-09-18 15:45:27</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7864,7 +7856,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:26</t>
+          <t>2026-09-18 16:20:26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7914,7 +7906,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:18</t>
+          <t>2026-09-18 16:45:57</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7964,7 +7956,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:20</t>
+          <t>2026-09-18 17:19:08</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7974,47 +7966,51 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>获取失败</t>
+          <t>「杨博文｜爱的初体验」是不是我的十六岁 注定要为__流泪</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Astra_杨博文</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:49:20</t>
+        </is>
+      </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>3042</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2032</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>143345</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:26</t>
+          <t>2026-09-18 17:45:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8058,13 +8054,13 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>-143345</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:36</t>
+          <t>2026-09-18 18:19:39</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8114,7 +8110,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:35</t>
+          <t>2026-09-18 18:45:11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8164,7 +8160,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:25</t>
+          <t>2026-09-18 19:18:26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8214,7 +8210,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:10</t>
+          <t>2026-09-18 19:44:18</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8264,7 +8260,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:46</t>
+          <t>2026-09-18 20:23:20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8314,12 +8310,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:18</t>
+          <t>2026-09-18 20:49:26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8364,12 +8360,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:21</t>
+          <t>2026-09-18 21:18:36</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8414,12 +8410,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:24</t>
+          <t>2026-09-18 21:45:35</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8464,12 +8460,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:21</t>
+          <t>2026-09-18 22:19:25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8514,12 +8510,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:20</t>
+          <t>2026-09-18 22:46:10</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8564,12 +8560,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:51</t>
+          <t>2026-09-18 23:18:46</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8614,12 +8610,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:02</t>
+          <t>2026-09-18 23:45:25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV1mX8z6NEzz</t>
+          <t>BV1k9gw6gE4U</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8664,7 +8660,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:54</t>
+          <t>2026-09-18 14:24:18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8714,7 +8710,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:33</t>
+          <t>2026-09-18 14:49:21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8764,7 +8760,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:05</t>
+          <t>2026-09-18 15:19:24</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8814,7 +8810,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:20</t>
+          <t>2026-09-18 15:45:21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8864,7 +8860,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:12</t>
+          <t>2026-09-18 16:20:20</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8914,7 +8910,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:14</t>
+          <t>2026-09-18 16:45:51</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8964,7 +8960,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:20</t>
+          <t>2026-09-18 17:19:02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9014,7 +9010,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:29</t>
+          <t>2026-09-18 17:44:54</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9064,7 +9060,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:29</t>
+          <t>2026-09-18 18:19:33</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9114,7 +9110,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:18</t>
+          <t>2026-09-18 18:45:05</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9164,7 +9160,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:04</t>
+          <t>2026-09-18 19:18:20</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9214,7 +9210,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:40</t>
+          <t>2026-09-18 19:44:12</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9264,12 +9260,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:19</t>
+          <t>2026-09-18 20:23:14</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9314,12 +9310,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-18 14:49:23</t>
+          <t>2026-09-18 20:49:20</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9364,12 +9360,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-18 15:19:26</t>
+          <t>2026-09-18 21:18:29</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9414,12 +9410,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:22</t>
+          <t>2026-09-18 21:45:29</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9464,12 +9460,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18 16:20:22</t>
+          <t>2026-09-18 22:19:18</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9514,12 +9510,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-18 16:45:52</t>
+          <t>2026-09-18 22:46:04</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9564,12 +9560,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18 17:19:03</t>
+          <t>2026-09-18 23:18:40</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9614,12 +9610,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-18 17:44:55</t>
+          <t>2026-09-18 23:45:19</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BV1qHbb6QErY</t>
+          <t>BV1mX8z6NEzz</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9664,7 +9660,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18 18:19:35</t>
+          <t>2026-09-18 14:24:19</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9714,7 +9710,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45:07</t>
+          <t>2026-09-18 14:49:23</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9764,7 +9760,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18 19:18:21</t>
+          <t>2026-09-18 15:19:26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9814,7 +9810,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-18 19:44:13</t>
+          <t>2026-09-18 15:45:22</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9864,7 +9860,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-18 20:23:16</t>
+          <t>2026-09-18 16:20:22</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9914,7 +9910,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-18 20:49:22</t>
+          <t>2026-09-18 16:45:52</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9964,7 +9960,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-18 21:18:31</t>
+          <t>2026-09-18 17:19:03</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10014,7 +10010,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-18 21:45:30</t>
+          <t>2026-09-18 17:44:55</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10064,7 +10060,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18 22:19:20</t>
+          <t>2026-09-18 18:19:35</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10114,7 +10110,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18 22:46:05</t>
+          <t>2026-09-18 18:45:07</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10164,7 +10160,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-18 23:18:42</t>
+          <t>2026-09-18 19:18:21</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10214,12 +10210,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:28</t>
+          <t>2026-09-18 19:44:13</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BV1r8eV6fE5N</t>
+          <t>BV1qHbb6QErY</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10264,12 +10260,12 @@
     <